--- a/tercier-financial-model.xlsx
+++ b/tercier-financial-model.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity Analysis" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -2958,8 +2958,9 @@
           <t>Founder salary (EUR/month)</t>
         </is>
       </c>
-      <c r="B75" s="144" t="n">
-        <v>4395.604395604396</v>
+      <c r="B75" s="144">
+        <f>B74/(12*$B$6)</f>
+        <v/>
       </c>
       <c r="C75" s="127" t="n"/>
       <c r="D75" s="136" t="inlineStr">
@@ -8391,8 +8392,9 @@
       <c r="D5" s="236" t="n">
         <v>4138544</v>
       </c>
-      <c r="E5" s="237" t="n">
-        <v>-0.194</v>
+      <c r="E5" s="237">
+        <f>D5/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" s="125">
@@ -8412,8 +8414,9 @@
       <c r="D6" s="239" t="n">
         <v>-6124507</v>
       </c>
-      <c r="E6" s="240" t="n">
-        <v>0.131</v>
+      <c r="E6" s="240">
+        <f>D6/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="125">
@@ -8433,8 +8436,9 @@
       <c r="D7" s="241" t="n">
         <v>4578819</v>
       </c>
-      <c r="E7" s="242" t="n">
-        <v>0.145</v>
+      <c r="E7" s="242">
+        <f>D7/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="125">
@@ -8454,8 +8458,9 @@
       <c r="D8" s="243" t="n">
         <v>-5337817</v>
       </c>
-      <c r="E8" s="244" t="n">
-        <v>-0.169</v>
+      <c r="E8" s="244">
+        <f>D8/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="125">
@@ -8475,8 +8480,9 @@
       <c r="D9" s="241" t="n">
         <v>4234861</v>
       </c>
-      <c r="E9" s="242" t="n">
-        <v>0.134</v>
+      <c r="E9" s="242">
+        <f>D9/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="125">
@@ -8496,8 +8502,9 @@
       <c r="D10" s="243" t="n">
         <v>-4503740</v>
       </c>
-      <c r="E10" s="244" t="n">
-        <v>-0.143</v>
+      <c r="E10" s="244">
+        <f>D10/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="125">
@@ -8517,8 +8524,9 @@
       <c r="D11" s="241" t="n">
         <v>506082</v>
       </c>
-      <c r="E11" s="242" t="n">
-        <v>0.016</v>
+      <c r="E11" s="242">
+        <f>D11/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="125">
@@ -8538,8 +8546,9 @@
       <c r="D12" s="243" t="n">
         <v>-711657</v>
       </c>
-      <c r="E12" s="244" t="n">
-        <v>-0.023</v>
+      <c r="E12" s="244">
+        <f>D12/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="125">
@@ -8559,8 +8568,9 @@
       <c r="D13" s="241" t="n">
         <v>112598</v>
       </c>
-      <c r="E13" s="242" t="n">
-        <v>0.004</v>
+      <c r="E13" s="242">
+        <f>D13/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="125">
@@ -8580,8 +8590,9 @@
       <c r="D14" s="239" t="n">
         <v>31009</v>
       </c>
-      <c r="E14" s="240" t="n">
-        <v>0.001</v>
+      <c r="E14" s="240">
+        <f>D14/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="125">
@@ -8601,8 +8612,9 @@
       <c r="D15" s="236" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="237" t="n">
-        <v>0</v>
+      <c r="E15" s="237">
+        <f>D15/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="125">
@@ -8622,8 +8634,9 @@
       <c r="D16" s="243" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="244" t="n">
-        <v>0</v>
+      <c r="E16" s="244">
+        <f>D16/31537836</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="125">
@@ -9434,22 +9447,25 @@
           <t>Founder salary</t>
         </is>
       </c>
-      <c r="B18" s="137" t="n">
-        <v>4396</v>
+      <c r="B18" s="137">
+        <f>Assumptions!B74/(12*Assumptions!$B$6)</f>
+        <v/>
       </c>
       <c r="C18" s="179">
         <f>B18/B10</f>
         <v/>
       </c>
-      <c r="D18" s="137" t="n">
-        <v>4396</v>
+      <c r="D18" s="137">
+        <f>Assumptions!B74/(12*Assumptions!$B$6)</f>
+        <v/>
       </c>
       <c r="E18" s="179">
         <f>D18/D10</f>
         <v/>
       </c>
-      <c r="F18" s="137" t="n">
-        <v>4396</v>
+      <c r="F18" s="137">
+        <f>Assumptions!B74/(12*Assumptions!$B$6)</f>
+        <v/>
       </c>
       <c r="G18" s="179">
         <f>F18/F10</f>
@@ -10379,16 +10395,16 @@
         </is>
       </c>
       <c r="B28" s="193">
-        <f>B27/8200</f>
+        <f>B27/B51</f>
         <v/>
       </c>
       <c r="C28" s="193">
-        <f>C27/8200</f>
+        <f>C27/B51</f>
         <v/>
       </c>
       <c r="D28" s="136" t="inlineStr">
         <is>
-          <t>Pre-revenue burn rate = ~EUR 9,725/mo</t>
+          <t>Seed / pre-revenue monthly burn</t>
         </is>
       </c>
       <c r="E28" s="127" t="n"/>
@@ -10724,7 +10740,7 @@
         </is>
       </c>
       <c r="B51" s="144" t="n">
-        <v>9725.274725274725</v>
+        <v>9725.27472527473</v>
       </c>
       <c r="C51" s="136" t="inlineStr">
         <is>
@@ -11118,11 +11134,11 @@
         </is>
       </c>
       <c r="B81" s="155">
-        <f>74*-3</f>
+        <f>-B74*3</f>
         <v/>
       </c>
       <c r="C81" s="155">
-        <f>74*-6</f>
+        <f>-C74*6</f>
         <v/>
       </c>
       <c r="D81" s="152" t="inlineStr">
@@ -11203,8 +11219,8 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B40:E40"/>
     <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B40:E40"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B43:E43"/>
@@ -11372,9 +11388,16 @@
           <t>Annual OTA commissions paid</t>
         </is>
       </c>
-      <c r="B9" s="127" t="n"/>
+      <c r="B9" s="127">
+        <f>25000000*0.18*0.5</f>
+        <v/>
+      </c>
       <c r="C9" s="127" t="n"/>
-      <c r="D9" s="127" t="n"/>
+      <c r="D9" s="127" t="inlineStr">
+        <is>
+          <t>EUR 25M × 18% × 50% = EUR 2.25M</t>
+        </is>
+      </c>
       <c r="E9" s="127" t="n"/>
       <c r="F9" s="127" t="n"/>
       <c r="G9" s="127" t="n"/>
@@ -11406,9 +11429,16 @@
           <t>Annual savings from 5% shift</t>
         </is>
       </c>
-      <c r="B11" s="127" t="n"/>
+      <c r="B11" s="127">
+        <f>B9*0.05</f>
+        <v/>
+      </c>
       <c r="C11" s="127" t="n"/>
-      <c r="D11" s="127" t="n"/>
+      <c r="D11" s="127" t="inlineStr">
+        <is>
+          <t>5% × OTA commissions</t>
+        </is>
+      </c>
       <c r="E11" s="127" t="n"/>
       <c r="F11" s="127" t="n"/>
       <c r="G11" s="127" t="n"/>
@@ -11419,9 +11449,8 @@
           <t>Platform annual cost (low)</t>
         </is>
       </c>
-      <c r="B12" s="202">
-        <f>25000000*0.18*0.5</f>
-        <v/>
+      <c r="B12" s="202" t="n">
+        <v>30000</v>
       </c>
       <c r="C12" s="127" t="n"/>
       <c r="D12" s="136" t="inlineStr">
@@ -11439,10 +11468,8 @@
           <t>Platform annual cost (high)</t>
         </is>
       </c>
-      <c r="B13" s="202" t="inlineStr">
-        <is>
-          <t>EUR 60,000</t>
-        </is>
+      <c r="B13" s="202" t="n">
+        <v>60000</v>
       </c>
       <c r="C13" s="127" t="n"/>
       <c r="D13" s="136" t="inlineStr">
@@ -11461,11 +11488,15 @@
         </is>
       </c>
       <c r="B14" s="148">
-        <f>B11*0.05</f>
+        <f>B11/B12</f>
         <v/>
       </c>
       <c r="C14" s="127" t="n"/>
-      <c r="D14" s="127" t="n"/>
+      <c r="D14" s="127" t="inlineStr">
+        <is>
+          <t>Annual savings / platform cost (low)</t>
+        </is>
+      </c>
       <c r="E14" s="127" t="n"/>
       <c r="F14" s="127" t="n"/>
       <c r="G14" s="127" t="n"/>
@@ -11507,11 +11538,18 @@
         </is>
       </c>
       <c r="B17" s="203">
-        <f>112500/30000</f>
-        <v/>
-      </c>
-      <c r="C17" s="127" t="n"/>
-      <c r="D17" s="127" t="n"/>
+        <f>3000*12</f>
+        <v/>
+      </c>
+      <c r="C17" s="127">
+        <f>8000*12</f>
+        <v/>
+      </c>
+      <c r="D17" s="127" t="inlineStr">
+        <is>
+          <t>Monthly × 12</t>
+        </is>
+      </c>
       <c r="E17" s="127" t="n"/>
       <c r="F17" s="127" t="n"/>
       <c r="G17" s="127" t="n"/>
@@ -11560,10 +11598,7 @@
     </row>
     <row r="20" ht="19.5" customHeight="1" s="125">
       <c r="A20" s="127" t="n"/>
-      <c r="B20" s="187">
-        <f>5500*12</f>
-        <v/>
-      </c>
+      <c r="B20" s="187" t="n"/>
       <c r="C20" s="127" t="n"/>
       <c r="D20" s="127" t="n"/>
       <c r="E20" s="127" t="n"/>
@@ -12694,7 +12729,7 @@
       <c r="D19" s="127" t="n"/>
       <c r="E19" s="136" t="inlineStr">
         <is>
-          <t>50-75+ target</t>
+          <t>100-150 hotels (business plan target)</t>
         </is>
       </c>
       <c r="F19" s="127" t="n"/>
@@ -13445,18 +13480,19 @@
     <row r="29" ht="19.5" customHeight="1" s="125">
       <c r="A29" s="134" t="inlineStr">
         <is>
-          <t>G&amp;C: Cash capital (CHF 200K max)</t>
+          <t>G&amp;C: Cash capital (initial seed range)</t>
         </is>
       </c>
       <c r="B29" s="143" t="n">
-        <v>222222</v>
+        <v>164835</v>
       </c>
       <c r="C29" s="136" t="n">
         <v>4</v>
       </c>
-      <c r="D29" s="143">
-        <f>B29*C29</f>
-        <v/>
+      <c r="D29" s="143" t="inlineStr">
+        <is>
+          <t>Corrected seed anchor at CHF 150K / 0.91 FX</t>
+        </is>
       </c>
       <c r="E29" s="127" t="n"/>
       <c r="F29" s="127" t="n"/>
@@ -13728,15 +13764,15 @@
         </is>
       </c>
       <c r="B43" s="179">
-        <f>SUM(B38:B41)</f>
+        <f>SUM(B39:B42)</f>
         <v/>
       </c>
       <c r="C43" s="179">
-        <f>SUM(C38:C41)</f>
+        <f>SUM(C39:C42)</f>
         <v/>
       </c>
       <c r="D43" s="179">
-        <f>SUM(D38:D41)</f>
+        <f>SUM(D39:D42)</f>
         <v/>
       </c>
       <c r="E43" s="127" t="n"/>
@@ -16614,7 +16650,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1" s="125">
       <c r="A3" s="124" t="inlineStr">
         <is>
           <t>Source: research/synthetic-survey/run-2026-03-22-business-plan-monte-carlo-v2/</t>
@@ -17489,7 +17525,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1" s="125">
       <c r="A3" s="124" t="inlineStr">
         <is>
           <t>Source: research/synthetic-survey/run-2026-03-22-business-plan-monte-carlo-v2/</t>
@@ -17692,58 +17728,22 @@
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="125">
-      <c r="A11" s="157" t="inlineStr">
-        <is>
-          <t>Month 48</t>
-        </is>
-      </c>
-      <c r="B11" s="215" t="n">
-        <v>254</v>
-      </c>
-      <c r="C11" s="215" t="n">
-        <v>320</v>
-      </c>
-      <c r="D11" s="215" t="n">
-        <v>342</v>
-      </c>
-      <c r="E11" s="215" t="n">
-        <v>362</v>
-      </c>
-      <c r="F11" s="215" t="n">
-        <v>391</v>
-      </c>
-      <c r="G11" s="157" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="A11" s="157" t="n"/>
+      <c r="B11" s="215" t="n"/>
+      <c r="C11" s="215" t="n"/>
+      <c r="D11" s="215" t="n"/>
+      <c r="E11" s="215" t="n"/>
+      <c r="F11" s="215" t="n"/>
+      <c r="G11" s="157" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="125">
-      <c r="A12" s="214" t="inlineStr">
-        <is>
-          <t>Month 60</t>
-        </is>
-      </c>
-      <c r="B12" s="216" t="n">
-        <v>318</v>
-      </c>
-      <c r="C12" s="216" t="n">
-        <v>332</v>
-      </c>
-      <c r="D12" s="216" t="n">
-        <v>358</v>
-      </c>
-      <c r="E12" s="216" t="n">
-        <v>426</v>
-      </c>
-      <c r="F12" s="216" t="n">
-        <v>498</v>
-      </c>
-      <c r="G12" s="214" t="inlineStr">
-        <is>
-          <t>+104</t>
-        </is>
-      </c>
+      <c r="A12" s="214" t="n"/>
+      <c r="B12" s="216" t="n"/>
+      <c r="C12" s="216" t="n"/>
+      <c r="D12" s="216" t="n"/>
+      <c r="E12" s="216" t="n"/>
+      <c r="F12" s="216" t="n"/>
+      <c r="G12" s="214" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="125">
       <c r="A14" s="163" t="inlineStr">
@@ -17931,31 +17931,13 @@
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="125">
-      <c r="A21" s="157" t="inlineStr">
-        <is>
-          <t>Month 60</t>
-        </is>
-      </c>
-      <c r="B21" s="215" t="n">
-        <v>8618089</v>
-      </c>
-      <c r="C21" s="215" t="n">
-        <v>9849256</v>
-      </c>
-      <c r="D21" s="215" t="n">
-        <v>11557506</v>
-      </c>
-      <c r="E21" s="215" t="n">
-        <v>14162706</v>
-      </c>
-      <c r="F21" s="215" t="n">
-        <v>17354168</v>
-      </c>
-      <c r="G21" s="157" t="inlineStr">
-        <is>
-          <t>+32%</t>
-        </is>
-      </c>
+      <c r="A21" s="157" t="n"/>
+      <c r="B21" s="215" t="n"/>
+      <c r="C21" s="215" t="n"/>
+      <c r="D21" s="215" t="n"/>
+      <c r="E21" s="215" t="n"/>
+      <c r="F21" s="215" t="n"/>
+      <c r="G21" s="157" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="125">
       <c r="A23" s="163" t="inlineStr">
@@ -18292,7 +18274,7 @@
     <row r="39" ht="15" customHeight="1" s="125">
       <c r="A39" s="163" t="inlineStr">
         <is>
-          <t>MONTHLY P&amp;L SNAPSHOT (P50, EUR)</t>
+          <t>ILLUSTRATIVE MONTHLY P&amp;L SNAPSHOT (legacy exploratory build, not canonical path table)</t>
         </is>
       </c>
       <c r="B39" s="164" t="n"/>
@@ -18774,42 +18756,42 @@
     <row r="61" ht="15" customHeight="1" s="125">
       <c r="A61" s="211" t="inlineStr">
         <is>
-          <t>Same capital (CHF 200K seed), same team ceiling (8 people). Difference: 5 acquisition channels compound.</t>
+          <t>Same seed structure (CHF 120-150K initial capital) plus a milestone-based angel tranche. Difference: more support on onboarding, integrations, and group expansion.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="125">
       <c r="A62" s="211" t="inlineStr">
         <is>
-          <t>Network (Amedeo/Corsaro): ~3.5 intros/mo, 67% conv. Direct: founder 0.5/mo → sales team 3.5/mo.</t>
+          <t>Network remains the first channel. The upside comes from stronger expansion and follow-on distribution support, not a different wedge.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" s="125">
       <c r="A63" s="211" t="inlineStr">
         <is>
-          <t>PLG starts M18 (~4/mo). Channel partners M24 (~3/mo). Inbound M12 (~2.5/mo).</t>
+          <t>Additional execution capacity starts after traction, rather than assuming cold-volume scale from day one.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" s="125">
       <c r="A64" s="211" t="inlineStr">
         <is>
-          <t>Group rollouts (portfolio deals) add lumpiness: probability-weighted 2-5 hotels per event.</t>
+          <t>Group rollouts remain the main step-function driver in the upside path.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" s="125">
       <c r="A65" s="211" t="inlineStr">
         <is>
-          <t>M36 P50: 162 hotels, EUR 4.46M ARR — business plan target of 100-150 is between P10 and P50.</t>
+          <t>M36 P50: 154 hotels, EUR 5.33M ARR — this is the canonical follow-on-angel path used in the business plan.</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" s="125">
       <c r="A66" s="211" t="inlineStr">
         <is>
-          <t>M60 P50: 358 hotels, EUR 11.6M ARR, EUR 63.6M exit at 5.5x. Rev/employee: EUR 1.4M.</t>
+          <t>M60 P50: 321 hotels, EUR 13.22M ARR, EUR 68.1M exit at 5.15x.</t>
         </is>
       </c>
     </row>

--- a/tercier-financial-model.xlsx
+++ b/tercier-financial-model.xlsx
@@ -12,16 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Investment &amp; Capital" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value Math" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAM-SAM-SOM" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equity &amp; Cap Table" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Funnel &amp; Acquisition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario A — Base Case" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario B — Upside" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario C — VC-Accelerated" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Validation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity Analysis" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Funnel &amp; Acquisition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario A — Base Case" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario B — Upside" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario C — VC-Accelerated" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Validation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity Analysis" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -2816,7 +2815,7 @@
       </c>
       <c r="D68" s="136" t="inlineStr">
         <is>
-          <t>SIGTAX: CHF 2-5K complex; low for 3-shareholder</t>
+          <t>SIGTAX: CHF 2-5K complex; low for a simple 3-founder setup</t>
         </is>
       </c>
       <c r="E68" s="143">
@@ -3186,7 +3185,7 @@
       </c>
       <c r="E87" s="136" t="inlineStr">
         <is>
-          <t>+ 2-4% ESOP. European remote; Zurich = EUR 12-18K.</t>
+          <t>European remote; Zurich = EUR 12-18K.</t>
         </is>
       </c>
       <c r="F87" s="127" t="n"/>
@@ -5582,1485 +5581,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:G79"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="36" customWidth="1" style="124" min="1" max="1"/>
-    <col width="16" customWidth="1" style="124" min="2" max="6"/>
-    <col width="30" customWidth="1" style="124" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="125">
-      <c r="A1" s="210" t="inlineStr">
-        <is>
-          <t>TERCIER — Scenario C: Historical VC-Accelerated (exploratory, P50 retained)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="125">
-      <c r="A2" s="211" t="inlineStr">
-        <is>
-          <t>Historical exploratory sheet retained for comparison only. Hotel milestones were reduced to the internally consistent P50 path used by the retained ARR / P&amp;L snapshot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="125">
-      <c r="A4" s="163" t="inlineStr">
-        <is>
-          <t>CAPITAL STRUCTURE</t>
-        </is>
-      </c>
-      <c r="B4" s="164" t="n"/>
-      <c r="C4" s="164" t="n"/>
-      <c r="D4" s="164" t="n"/>
-      <c r="E4" s="164" t="n"/>
-      <c r="F4" s="164" t="n"/>
-      <c r="G4" s="164" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="125">
-      <c r="A5" s="212" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B5" s="218" t="inlineStr">
-        <is>
-          <t>Amount (EUR)</t>
-        </is>
-      </c>
-      <c r="C5" s="218" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="D5" s="218" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="E5" s="218" t="n"/>
-      <c r="F5" s="218" t="n"/>
-      <c r="G5" s="218" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="125">
-      <c r="A6" s="214" t="inlineStr">
-        <is>
-          <t>Seed (CHF 150K → EUR)</t>
-        </is>
-      </c>
-      <c r="B6" s="216" t="n">
-        <v>164835</v>
-      </c>
-      <c r="C6" s="214" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="D6" s="214" t="inlineStr">
-        <is>
-          <t>Guffanti/Corsaro operator seed</t>
-        </is>
-      </c>
-      <c r="E6" s="214" t="n"/>
-      <c r="F6" s="214" t="n"/>
-      <c r="G6" s="214" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="125">
-      <c r="A7" s="157" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="B7" s="215" t="n">
-        <v>55556</v>
-      </c>
-      <c r="C7" s="157" t="inlineStr">
-        <is>
-          <t>M0</t>
-        </is>
-      </c>
-      <c r="D7" s="157" t="inlineStr">
-        <is>
-          <t>AG incorporation</t>
-        </is>
-      </c>
-      <c r="E7" s="157" t="n"/>
-      <c r="F7" s="157" t="n"/>
-      <c r="G7" s="157" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="125">
-      <c r="A8" s="214" t="inlineStr">
-        <is>
-          <t>Series A (strategic)</t>
-        </is>
-      </c>
-      <c r="B8" s="216" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="C8" s="214" t="inlineStr">
-        <is>
-          <t>M27</t>
-        </is>
-      </c>
-      <c r="D8" s="214" t="inlineStr">
-        <is>
-          <t>Hospitality-specific investor. Raise from strength.</t>
-        </is>
-      </c>
-      <c r="E8" s="214" t="n"/>
-      <c r="F8" s="214" t="n"/>
-      <c r="G8" s="214" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="125">
-      <c r="A9" s="160" t="inlineStr">
-        <is>
-          <t>Total capital</t>
-        </is>
-      </c>
-      <c r="B9" s="222" t="n">
-        <v>4277778</v>
-      </c>
-      <c r="C9" s="160" t="n"/>
-      <c r="D9" s="160" t="inlineStr">
-        <is>
-          <t>vs EUR 277K in operator-seeded paths</t>
-        </is>
-      </c>
-      <c r="E9" s="160" t="n"/>
-      <c r="F9" s="160" t="n"/>
-      <c r="G9" s="160" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="125">
-      <c r="A11" s="163" t="inlineStr">
-        <is>
-          <t>HOTEL MILESTONES (P50 path retained from monthly snapshot)</t>
-        </is>
-      </c>
-      <c r="B11" s="164" t="n"/>
-      <c r="C11" s="164" t="n"/>
-      <c r="D11" s="164" t="n"/>
-      <c r="E11" s="164" t="n"/>
-      <c r="F11" s="164" t="n"/>
-      <c r="G11" s="164" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="125">
-      <c r="A12" s="212" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="B12" s="165" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="C12" s="165" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D12" s="165" t="n"/>
-      <c r="E12" s="165" t="inlineStr">
-        <is>
-          <t>P75</t>
-        </is>
-      </c>
-      <c r="F12" s="165" t="inlineStr">
-        <is>
-          <t>P90</t>
-        </is>
-      </c>
-      <c r="G12" s="165" t="inlineStr">
-        <is>
-          <t>vs Scenario A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="125">
-      <c r="A13" s="214" t="inlineStr">
-        <is>
-          <t>Month 6</t>
-        </is>
-      </c>
-      <c r="B13" s="223" t="n">
-        <v>14</v>
-      </c>
-      <c r="C13" s="223" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D13" s="216" t="n"/>
-      <c r="E13" s="223" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="223" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G13" s="214" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="125">
-      <c r="A14" s="157" t="inlineStr">
-        <is>
-          <t>Month 12</t>
-        </is>
-      </c>
-      <c r="B14" s="215" t="n">
-        <v>21</v>
-      </c>
-      <c r="C14" s="224" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D14" s="215" t="n"/>
-      <c r="E14" s="224" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="215" t="n">
-        <v>33</v>
-      </c>
-      <c r="G14" s="157" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="125">
-      <c r="A15" s="214" t="inlineStr">
-        <is>
-          <t>Month 18</t>
-        </is>
-      </c>
-      <c r="B15" s="216" t="n">
-        <v>62</v>
-      </c>
-      <c r="C15" s="225" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D15" s="216" t="n"/>
-      <c r="E15" s="225" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="216" t="n">
-        <v>48</v>
-      </c>
-      <c r="G15" s="214" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="125">
-      <c r="A16" s="157" t="inlineStr">
-        <is>
-          <t>Month 24</t>
-        </is>
-      </c>
-      <c r="B16" s="215" t="n">
-        <v>99</v>
-      </c>
-      <c r="C16" s="215" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D16" s="215" t="n"/>
-      <c r="E16" s="215" t="n">
-        <v>115</v>
-      </c>
-      <c r="F16" s="215" t="n">
-        <v>129</v>
-      </c>
-      <c r="G16" s="157" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="125">
-      <c r="A17" s="214" t="inlineStr">
-        <is>
-          <t>Month 36</t>
-        </is>
-      </c>
-      <c r="B17" s="216" t="n">
-        <v>502</v>
-      </c>
-      <c r="C17" s="225" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D17" s="216" t="n"/>
-      <c r="E17" s="225" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="216" t="n">
-        <v>135</v>
-      </c>
-      <c r="G17" s="214" t="inlineStr">
-        <is>
-          <t>+28</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="125">
-      <c r="A18" s="157" t="inlineStr">
-        <is>
-          <t>Month 48</t>
-        </is>
-      </c>
-      <c r="B18" s="215" t="n">
-        <v>818</v>
-      </c>
-      <c r="C18" s="215" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D18" s="215" t="n"/>
-      <c r="E18" s="215" t="n">
-        <v>931</v>
-      </c>
-      <c r="F18" s="215" t="n">
-        <v>1038</v>
-      </c>
-      <c r="G18" s="157" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="125">
-      <c r="A19" s="214" t="inlineStr">
-        <is>
-          <t>Month 60</t>
-        </is>
-      </c>
-      <c r="B19" s="216" t="n">
-        <v>886</v>
-      </c>
-      <c r="C19" s="225" t="inlineStr">
-        <is>
-          <t>Retained P50 path</t>
-        </is>
-      </c>
-      <c r="D19" s="216" t="n"/>
-      <c r="E19" s="225" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="216" t="n">
-        <v>424</v>
-      </c>
-      <c r="G19" s="214" t="inlineStr">
-        <is>
-          <t>+128</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="125">
-      <c r="A21" s="163" t="inlineStr">
-        <is>
-          <t>ARR TRAJECTORY (EUR)</t>
-        </is>
-      </c>
-      <c r="B21" s="164" t="n"/>
-      <c r="C21" s="164" t="n"/>
-      <c r="D21" s="164" t="n"/>
-      <c r="E21" s="164" t="n"/>
-      <c r="F21" s="164" t="n"/>
-      <c r="G21" s="164" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="125">
-      <c r="A22" s="212" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="B22" s="165" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="C22" s="165" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="D22" s="165" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="E22" s="165" t="inlineStr">
-        <is>
-          <t>P75</t>
-        </is>
-      </c>
-      <c r="F22" s="165" t="inlineStr">
-        <is>
-          <t>P90</t>
-        </is>
-      </c>
-      <c r="G22" s="165" t="inlineStr">
-        <is>
-          <t>vs Scenario A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="125">
-      <c r="A23" s="214" t="inlineStr">
-        <is>
-          <t>Month 12</t>
-        </is>
-      </c>
-      <c r="B23" s="216" t="n">
-        <v>323423</v>
-      </c>
-      <c r="C23" s="216" t="n">
-        <v>391209</v>
-      </c>
-      <c r="D23" s="216" t="n">
-        <v>486928</v>
-      </c>
-      <c r="E23" s="216" t="n">
-        <v>606000</v>
-      </c>
-      <c r="F23" s="216" t="n">
-        <v>733277</v>
-      </c>
-      <c r="G23" s="214" t="inlineStr">
-        <is>
-          <t>+5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="125">
-      <c r="A24" s="157" t="inlineStr">
-        <is>
-          <t>Month 18</t>
-        </is>
-      </c>
-      <c r="B24" s="215" t="n">
-        <v>989324</v>
-      </c>
-      <c r="C24" s="215" t="n">
-        <v>1246506</v>
-      </c>
-      <c r="D24" s="215" t="n">
-        <v>1547509</v>
-      </c>
-      <c r="E24" s="215" t="n">
-        <v>1878612</v>
-      </c>
-      <c r="F24" s="215" t="n">
-        <v>2202507</v>
-      </c>
-      <c r="G24" s="157" t="inlineStr">
-        <is>
-          <t>+99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="125">
-      <c r="A25" s="214" t="inlineStr">
-        <is>
-          <t>Month 24</t>
-        </is>
-      </c>
-      <c r="B25" s="216" t="n">
-        <v>1703047</v>
-      </c>
-      <c r="C25" s="216" t="n">
-        <v>2076296</v>
-      </c>
-      <c r="D25" s="216" t="n">
-        <v>2582714</v>
-      </c>
-      <c r="E25" s="216" t="n">
-        <v>3173308</v>
-      </c>
-      <c r="F25" s="216" t="n">
-        <v>3767253</v>
-      </c>
-      <c r="G25" s="214" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="125">
-      <c r="A26" s="157" t="inlineStr">
-        <is>
-          <t>Month 36</t>
-        </is>
-      </c>
-      <c r="B26" s="215" t="n">
-        <v>10387079</v>
-      </c>
-      <c r="C26" s="215" t="n">
-        <v>13212060</v>
-      </c>
-      <c r="D26" s="215" t="n">
-        <v>16735554</v>
-      </c>
-      <c r="E26" s="215" t="n">
-        <v>20665691</v>
-      </c>
-      <c r="F26" s="215" t="n">
-        <v>24553645</v>
-      </c>
-      <c r="G26" s="157" t="inlineStr">
-        <is>
-          <t>+549%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="125">
-      <c r="A27" s="214" t="inlineStr">
-        <is>
-          <t>Month 48</t>
-        </is>
-      </c>
-      <c r="B27" s="216" t="n">
-        <v>22783966</v>
-      </c>
-      <c r="C27" s="216" t="n">
-        <v>25639903</v>
-      </c>
-      <c r="D27" s="216" t="n">
-        <v>29604998</v>
-      </c>
-      <c r="E27" s="216" t="n">
-        <v>34852501</v>
-      </c>
-      <c r="F27" s="216" t="n">
-        <v>40716173</v>
-      </c>
-      <c r="G27" s="214" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="125">
-      <c r="A28" s="157" t="inlineStr">
-        <is>
-          <t>Month 60</t>
-        </is>
-      </c>
-      <c r="B28" s="215" t="n">
-        <v>24926447</v>
-      </c>
-      <c r="C28" s="215" t="n">
-        <v>28069088</v>
-      </c>
-      <c r="D28" s="215" t="n">
-        <v>34055136</v>
-      </c>
-      <c r="E28" s="215" t="n">
-        <v>44751357</v>
-      </c>
-      <c r="F28" s="215" t="n">
-        <v>55550176</v>
-      </c>
-      <c r="G28" s="157" t="inlineStr">
-        <is>
-          <t>+288%</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="125">
-      <c r="A30" s="163" t="inlineStr">
-        <is>
-          <t>MONTHLY P&amp;L SNAPSHOT (P50, EUR)</t>
-        </is>
-      </c>
-      <c r="B30" s="164" t="n"/>
-      <c r="C30" s="164" t="n"/>
-      <c r="D30" s="164" t="n"/>
-      <c r="E30" s="164" t="n"/>
-      <c r="F30" s="164" t="n"/>
-      <c r="G30" s="164" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="125">
-      <c r="A31" s="212" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B31" s="218" t="inlineStr">
-        <is>
-          <t>MRR</t>
-        </is>
-      </c>
-      <c r="C31" s="218" t="inlineStr">
-        <is>
-          <t>Hotels</t>
-        </is>
-      </c>
-      <c r="D31" s="218" t="inlineStr">
-        <is>
-          <t>Total Costs</t>
-        </is>
-      </c>
-      <c r="E31" s="218" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="F31" s="218" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="G31" s="218" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="125">
-      <c r="A32" s="214" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B32" s="216" t="n">
-        <v>3635</v>
-      </c>
-      <c r="C32" s="216" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="216" t="n">
-        <v>11173</v>
-      </c>
-      <c r="E32" s="216" t="n">
-        <v>-7972</v>
-      </c>
-      <c r="F32" s="216" t="n">
-        <v>269806</v>
-      </c>
-      <c r="G32" s="216" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="125">
-      <c r="A33" s="157" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B33" s="215" t="n">
-        <v>26339</v>
-      </c>
-      <c r="C33" s="215" t="n">
-        <v>14</v>
-      </c>
-      <c r="D33" s="215" t="n">
-        <v>14945</v>
-      </c>
-      <c r="E33" s="215" t="n">
-        <v>7381</v>
-      </c>
-      <c r="F33" s="215" t="n">
-        <v>269850</v>
-      </c>
-      <c r="G33" s="215" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="125">
-      <c r="A34" s="214" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="B34" s="216" t="n">
-        <v>40577</v>
-      </c>
-      <c r="C34" s="216" t="n">
-        <v>21</v>
-      </c>
-      <c r="D34" s="216" t="n">
-        <v>35321</v>
-      </c>
-      <c r="E34" s="216" t="n">
-        <v>5207</v>
-      </c>
-      <c r="F34" s="216" t="n">
-        <v>299813</v>
-      </c>
-      <c r="G34" s="216" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="125">
-      <c r="A35" s="157" t="inlineStr">
-        <is>
-          <t>M18</t>
-        </is>
-      </c>
-      <c r="B35" s="215" t="n">
-        <v>128959</v>
-      </c>
-      <c r="C35" s="215" t="n">
-        <v>62</v>
-      </c>
-      <c r="D35" s="215" t="n">
-        <v>59454</v>
-      </c>
-      <c r="E35" s="215" t="n">
-        <v>70422</v>
-      </c>
-      <c r="F35" s="215" t="n">
-        <v>485101</v>
-      </c>
-      <c r="G35" s="215" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="125">
-      <c r="A36" s="214" t="inlineStr">
-        <is>
-          <t>M24</t>
-        </is>
-      </c>
-      <c r="B36" s="216" t="n">
-        <v>215226</v>
-      </c>
-      <c r="C36" s="216" t="n">
-        <v>99</v>
-      </c>
-      <c r="D36" s="216" t="n">
-        <v>63570</v>
-      </c>
-      <c r="E36" s="216" t="n">
-        <v>151393</v>
-      </c>
-      <c r="F36" s="216" t="n">
-        <v>1132290</v>
-      </c>
-      <c r="G36" s="216" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="125">
-      <c r="A37" s="226" t="inlineStr">
-        <is>
-          <t>M27</t>
-        </is>
-      </c>
-      <c r="B37" s="227" t="n">
-        <v>281531</v>
-      </c>
-      <c r="C37" s="227" t="n">
-        <v>128</v>
-      </c>
-      <c r="D37" s="227" t="n">
-        <v>67755</v>
-      </c>
-      <c r="E37" s="227" t="n">
-        <v>213921</v>
-      </c>
-      <c r="F37" s="227" t="n">
-        <v>5708048</v>
-      </c>
-      <c r="G37" s="228" t="inlineStr">
-        <is>
-          <t>← Series A</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="125">
-      <c r="A38" s="214" t="inlineStr">
-        <is>
-          <t>M30</t>
-        </is>
-      </c>
-      <c r="B38" s="216" t="n">
-        <v>390113</v>
-      </c>
-      <c r="C38" s="216" t="n">
-        <v>172</v>
-      </c>
-      <c r="D38" s="216" t="n">
-        <v>112654</v>
-      </c>
-      <c r="E38" s="216" t="n">
-        <v>276644</v>
-      </c>
-      <c r="F38" s="216" t="n">
-        <v>6496623</v>
-      </c>
-      <c r="G38" s="216" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="125">
-      <c r="A39" s="157" t="inlineStr">
-        <is>
-          <t>M33</t>
-        </is>
-      </c>
-      <c r="B39" s="215" t="n">
-        <v>649097</v>
-      </c>
-      <c r="C39" s="215" t="n">
-        <v>240</v>
-      </c>
-      <c r="D39" s="215" t="n">
-        <v>127799</v>
-      </c>
-      <c r="E39" s="215" t="n">
-        <v>521135</v>
-      </c>
-      <c r="F39" s="215" t="n">
-        <v>7636526</v>
-      </c>
-      <c r="G39" s="215" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="125">
-      <c r="A40" s="214" t="inlineStr">
-        <is>
-          <t>M36</t>
-        </is>
-      </c>
-      <c r="B40" s="216" t="n">
-        <v>1394629</v>
-      </c>
-      <c r="C40" s="216" t="n">
-        <v>502</v>
-      </c>
-      <c r="D40" s="216" t="n">
-        <v>172481</v>
-      </c>
-      <c r="E40" s="216" t="n">
-        <v>1221982</v>
-      </c>
-      <c r="F40" s="216" t="n">
-        <v>10522913</v>
-      </c>
-      <c r="G40" s="216" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="125">
-      <c r="A41" s="157" t="inlineStr">
-        <is>
-          <t>M42</t>
-        </is>
-      </c>
-      <c r="B41" s="215" t="n">
-        <v>2248036</v>
-      </c>
-      <c r="C41" s="215" t="n">
-        <v>780</v>
-      </c>
-      <c r="D41" s="215" t="n">
-        <v>222336</v>
-      </c>
-      <c r="E41" s="215" t="n">
-        <v>2024848</v>
-      </c>
-      <c r="F41" s="215" t="n">
-        <v>21123515</v>
-      </c>
-      <c r="G41" s="215" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="125">
-      <c r="A42" s="214" t="inlineStr">
-        <is>
-          <t>M48</t>
-        </is>
-      </c>
-      <c r="B42" s="216" t="n">
-        <v>2467083</v>
-      </c>
-      <c r="C42" s="216" t="n">
-        <v>818</v>
-      </c>
-      <c r="D42" s="216" t="n">
-        <v>235833</v>
-      </c>
-      <c r="E42" s="216" t="n">
-        <v>2232438</v>
-      </c>
-      <c r="F42" s="216" t="n">
-        <v>33707725</v>
-      </c>
-      <c r="G42" s="216" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="125">
-      <c r="A43" s="157" t="inlineStr">
-        <is>
-          <t>M54</t>
-        </is>
-      </c>
-      <c r="B43" s="215" t="n">
-        <v>2669239</v>
-      </c>
-      <c r="C43" s="215" t="n">
-        <v>858</v>
-      </c>
-      <c r="D43" s="215" t="n">
-        <v>247128</v>
-      </c>
-      <c r="E43" s="215" t="n">
-        <v>2421366</v>
-      </c>
-      <c r="F43" s="215" t="n">
-        <v>47666864</v>
-      </c>
-      <c r="G43" s="215" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="125">
-      <c r="A44" s="214" t="inlineStr">
-        <is>
-          <t>M60</t>
-        </is>
-      </c>
-      <c r="B44" s="216" t="n">
-        <v>2837928</v>
-      </c>
-      <c r="C44" s="216" t="n">
-        <v>886</v>
-      </c>
-      <c r="D44" s="216" t="n">
-        <v>257064</v>
-      </c>
-      <c r="E44" s="216" t="n">
-        <v>2581774</v>
-      </c>
-      <c r="F44" s="216" t="n">
-        <v>62491641</v>
-      </c>
-      <c r="G44" s="216" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="125">
-      <c r="A46" s="163" t="inlineStr">
-        <is>
-          <t>MILESTONE PROBABILITIES</t>
-        </is>
-      </c>
-      <c r="B46" s="164" t="n"/>
-      <c r="C46" s="164" t="n"/>
-      <c r="D46" s="164" t="n"/>
-      <c r="E46" s="164" t="n"/>
-      <c r="F46" s="164" t="n"/>
-      <c r="G46" s="164" t="n"/>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="125">
-      <c r="A47" s="212" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="B47" s="218" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="C47" s="218" t="n"/>
-      <c r="D47" s="218" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="E47" s="218" t="n"/>
-      <c r="F47" s="218" t="n"/>
-      <c r="G47" s="218" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="125">
-      <c r="A48" s="214" t="inlineStr">
-        <is>
-          <t>5 hotels by M12</t>
-        </is>
-      </c>
-      <c r="B48" s="219" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="214" t="n"/>
-      <c r="D48" s="214" t="n"/>
-      <c r="E48" s="214" t="n"/>
-      <c r="F48" s="214" t="n"/>
-      <c r="G48" s="214" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="125">
-      <c r="A49" s="157" t="inlineStr">
-        <is>
-          <t>€25K MRR by M18</t>
-        </is>
-      </c>
-      <c r="B49" s="220" t="n">
-        <v>0.9999</v>
-      </c>
-      <c r="C49" s="157" t="n"/>
-      <c r="D49" s="157" t="n"/>
-      <c r="E49" s="157" t="n"/>
-      <c r="F49" s="157" t="n"/>
-      <c r="G49" s="157" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="125">
-      <c r="A50" s="214" t="inlineStr">
-        <is>
-          <t>€75K MRR by M24</t>
-        </is>
-      </c>
-      <c r="B50" s="219" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="C50" s="214" t="n"/>
-      <c r="D50" s="214" t="n"/>
-      <c r="E50" s="214" t="n"/>
-      <c r="F50" s="214" t="n"/>
-      <c r="G50" s="214" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="125">
-      <c r="A51" s="157" t="inlineStr">
-        <is>
-          <t>€1M ARR by M24</t>
-        </is>
-      </c>
-      <c r="B51" s="220" t="n">
-        <v>0.9981</v>
-      </c>
-      <c r="C51" s="157" t="n"/>
-      <c r="D51" s="157" t="n"/>
-      <c r="E51" s="157" t="n"/>
-      <c r="F51" s="157" t="n"/>
-      <c r="G51" s="157" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="125">
-      <c r="A52" s="214" t="inlineStr">
-        <is>
-          <t>€5M ARR by M36</t>
-        </is>
-      </c>
-      <c r="B52" s="219" t="n">
-        <v>0.9978</v>
-      </c>
-      <c r="C52" s="214" t="n"/>
-      <c r="D52" s="214" t="n"/>
-      <c r="E52" s="214" t="n"/>
-      <c r="F52" s="214" t="n"/>
-      <c r="G52" s="214" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="125">
-      <c r="A53" s="157" t="inlineStr">
-        <is>
-          <t>€10M ARR by M48</t>
-        </is>
-      </c>
-      <c r="B53" s="220" t="n">
-        <v>0.9989</v>
-      </c>
-      <c r="C53" s="157" t="n"/>
-      <c r="D53" s="157" t="n"/>
-      <c r="E53" s="157" t="n"/>
-      <c r="F53" s="157" t="n"/>
-      <c r="G53" s="157" t="n"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="125">
-      <c r="A54" s="214" t="inlineStr">
-        <is>
-          <t>€15M ARR by M60</t>
-        </is>
-      </c>
-      <c r="B54" s="219" t="n">
-        <v>0.9972</v>
-      </c>
-      <c r="C54" s="214" t="n"/>
-      <c r="D54" s="214" t="n"/>
-      <c r="E54" s="214" t="n"/>
-      <c r="F54" s="214" t="n"/>
-      <c r="G54" s="214" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="125">
-      <c r="A55" s="157" t="inlineStr">
-        <is>
-          <t>€20M ARR by M60</t>
-        </is>
-      </c>
-      <c r="B55" s="220" t="n">
-        <v>0.9892</v>
-      </c>
-      <c r="C55" s="157" t="n"/>
-      <c r="D55" s="157" t="n"/>
-      <c r="E55" s="157" t="n"/>
-      <c r="F55" s="157" t="n"/>
-      <c r="G55" s="157" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="125">
-      <c r="A56" s="214" t="inlineStr">
-        <is>
-          <t>Breakeven by M9</t>
-        </is>
-      </c>
-      <c r="B56" s="219" t="n">
-        <v>0.9782</v>
-      </c>
-      <c r="C56" s="214" t="n"/>
-      <c r="D56" s="214" t="n"/>
-      <c r="E56" s="214" t="n"/>
-      <c r="F56" s="214" t="n"/>
-      <c r="G56" s="214" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="125">
-      <c r="A57" s="157" t="inlineStr">
-        <is>
-          <t>Breakeven by M12</t>
-        </is>
-      </c>
-      <c r="B57" s="220" t="n">
-        <v>0.9855</v>
-      </c>
-      <c r="C57" s="157" t="n"/>
-      <c r="D57" s="157" t="n"/>
-      <c r="E57" s="157" t="n"/>
-      <c r="F57" s="157" t="n"/>
-      <c r="G57" s="157" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="125">
-      <c r="A58" s="214" t="inlineStr">
-        <is>
-          <t>Cash negative ever</t>
-        </is>
-      </c>
-      <c r="B58" s="219" t="n">
-        <v>0.0007</v>
-      </c>
-      <c r="C58" s="214" t="n"/>
-      <c r="D58" s="214" t="n"/>
-      <c r="E58" s="214" t="n"/>
-      <c r="F58" s="214" t="n"/>
-      <c r="G58" s="214" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="125">
-      <c r="A59" s="157" t="inlineStr">
-        <is>
-          <t>€100M exit (4x) by M60</t>
-        </is>
-      </c>
-      <c r="B59" s="220" t="n">
-        <v>0.8966</v>
-      </c>
-      <c r="C59" s="157" t="n"/>
-      <c r="D59" s="157" t="n"/>
-      <c r="E59" s="157" t="n"/>
-      <c r="F59" s="157" t="n"/>
-      <c r="G59" s="157" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="125">
-      <c r="A60" s="214" t="inlineStr">
-        <is>
-          <t>€100M exit (5.5x) by M60</t>
-        </is>
-      </c>
-      <c r="B60" s="219" t="n">
-        <v>0.9933</v>
-      </c>
-      <c r="C60" s="214" t="n"/>
-      <c r="D60" s="214" t="n"/>
-      <c r="E60" s="214" t="n"/>
-      <c r="F60" s="214" t="n"/>
-      <c r="G60" s="214" t="n"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="125">
-      <c r="A61" s="157" t="inlineStr">
-        <is>
-          <t>€100M exit (7x) by M60</t>
-        </is>
-      </c>
-      <c r="B61" s="220" t="n">
-        <v>0.9977</v>
-      </c>
-      <c r="C61" s="157" t="n"/>
-      <c r="D61" s="157" t="n"/>
-      <c r="E61" s="157" t="n"/>
-      <c r="F61" s="157" t="n"/>
-      <c r="G61" s="157" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="125">
-      <c r="A62" s="163" t="inlineStr">
-        <is>
-          <t>EXIT VALUATION AT MONTH 60 (EUR)</t>
-        </is>
-      </c>
-      <c r="B62" s="164" t="n"/>
-      <c r="C62" s="164" t="n"/>
-      <c r="D62" s="164" t="n"/>
-      <c r="E62" s="164" t="n"/>
-      <c r="F62" s="164" t="n"/>
-      <c r="G62" s="164" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="125">
-      <c r="A63" s="212" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B63" s="218" t="inlineStr">
-        <is>
-          <t>P10</t>
-        </is>
-      </c>
-      <c r="C63" s="218" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="D63" s="218" t="inlineStr">
-        <is>
-          <t>P50</t>
-        </is>
-      </c>
-      <c r="E63" s="218" t="inlineStr">
-        <is>
-          <t>P75</t>
-        </is>
-      </c>
-      <c r="F63" s="218" t="inlineStr">
-        <is>
-          <t>P90</t>
-        </is>
-      </c>
-      <c r="G63" s="218" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="125">
-      <c r="A64" s="214" t="inlineStr">
-        <is>
-          <t>Exit (5.5x ARR)</t>
-        </is>
-      </c>
-      <c r="B64" s="216" t="n">
-        <v>137095457</v>
-      </c>
-      <c r="C64" s="216" t="n">
-        <v>154379983</v>
-      </c>
-      <c r="D64" s="216" t="n">
-        <v>187303250</v>
-      </c>
-      <c r="E64" s="216" t="n">
-        <v>246132461</v>
-      </c>
-      <c r="F64" s="216" t="n">
-        <v>305525966</v>
-      </c>
-      <c r="G64" s="214" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="125">
-      <c r="A65" s="157" t="inlineStr">
-        <is>
-          <t>EUR 100M+ exit prob</t>
-        </is>
-      </c>
-      <c r="B65" s="157" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="C65" s="157" t="n"/>
-      <c r="D65" s="157" t="inlineStr">
-        <is>
-          <t>P10 is EUR 137M at 5.5x. Highly likely to clear EUR 100M.</t>
-        </is>
-      </c>
-      <c r="E65" s="157" t="n"/>
-      <c r="F65" s="157" t="n"/>
-      <c r="G65" s="157" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="125">
-      <c r="A67" s="163" t="inlineStr">
-        <is>
-          <t>AI-NATIVE EFFICIENCY METRICS</t>
-        </is>
-      </c>
-      <c r="B67" s="164" t="n"/>
-      <c r="C67" s="164" t="n"/>
-      <c r="D67" s="164" t="n"/>
-      <c r="E67" s="164" t="n"/>
-      <c r="F67" s="164" t="n"/>
-      <c r="G67" s="164" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="125">
-      <c r="A68" s="214" t="inlineStr">
-        <is>
-          <t>Max team size</t>
-        </is>
-      </c>
-      <c r="B68" s="216" t="n">
-        <v>18</v>
-      </c>
-      <c r="C68" s="214" t="n"/>
-      <c r="D68" s="214" t="inlineStr">
-        <is>
-          <t>vs 8 (operator) or 60 (full VC). AI replaces headcount.</t>
-        </is>
-      </c>
-      <c r="E68" s="214" t="n"/>
-      <c r="F68" s="214" t="n"/>
-      <c r="G68" s="214" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="125">
-      <c r="A69" s="157" t="inlineStr">
-        <is>
-          <t>Rev/employee (P50)</t>
-        </is>
-      </c>
-      <c r="B69" s="215" t="n">
-        <v>1891952</v>
-      </c>
-      <c r="C69" s="157" t="n"/>
-      <c r="D69" s="157" t="inlineStr">
-        <is>
-          <t>EUR 34M ARR / 18 people. Best-in-class vertical SaaS.</t>
-        </is>
-      </c>
-      <c r="E69" s="157" t="n"/>
-      <c r="F69" s="157" t="n"/>
-      <c r="G69" s="157" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="125">
-      <c r="A70" s="214" t="inlineStr">
-        <is>
-          <t>Capital efficiency</t>
-        </is>
-      </c>
-      <c r="B70" s="214" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="C70" s="214" t="n"/>
-      <c r="D70" s="214" t="inlineStr">
-        <is>
-          <t>EUR 34M ARR on EUR 4.3M total capital.</t>
-        </is>
-      </c>
-      <c r="E70" s="214" t="n"/>
-      <c r="F70" s="214" t="n"/>
-      <c r="G70" s="214" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="125">
-      <c r="A71" s="157" t="inlineStr">
-        <is>
-          <t>vs Path B (full VC)</t>
-        </is>
-      </c>
-      <c r="B71" s="157" t="inlineStr">
-        <is>
-          <t>60 people</t>
-        </is>
-      </c>
-      <c r="C71" s="157" t="n"/>
-      <c r="D71" s="157" t="inlineStr">
-        <is>
-          <t>EUR 99M ARR but EUR 42M capital and 60 team.</t>
-        </is>
-      </c>
-      <c r="E71" s="157" t="n"/>
-      <c r="F71" s="157" t="n"/>
-      <c r="G71" s="157" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="125">
-      <c r="A73" s="163" t="inlineStr">
-        <is>
-          <t>SCENARIO NARRATIVE</t>
-        </is>
-      </c>
-      <c r="B73" s="164" t="n"/>
-      <c r="C73" s="164" t="n"/>
-      <c r="D73" s="164" t="n"/>
-      <c r="E73" s="164" t="n"/>
-      <c r="F73" s="164" t="n"/>
-      <c r="G73" s="164" t="n"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="125">
-      <c r="A74" s="211" t="inlineStr">
-        <is>
-          <t>Path C is the recommended strategic path. Same early trajectory as operator-seeded (M1-24 identical).</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="125">
-      <c r="A75" s="211" t="inlineStr">
-        <is>
-          <t>EUR 4M strategic raise at M27 from a hospitality-specific investor (not a generalist VC).</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="125">
-      <c r="A76" s="211" t="inlineStr">
-        <is>
-          <t>Capital buys: faster PMS integrations, accelerated GTM (5 markets vs 2), portfolio expansion deals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="125">
-      <c r="A77" s="211" t="inlineStr">
-        <is>
-          <t>Team grows to 18 (not 60) — AI-native model means margin stays high (66-75%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="125">
-      <c r="A78" s="211" t="inlineStr">
-        <is>
-          <t>M36 P50: 502 hotels, EUR 16.7M ARR. M60 P50: 886 hotels, EUR 34M ARR, EUR 187M exit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="125">
-      <c r="A79" s="211" t="inlineStr">
-        <is>
-          <t>NOTE: M33+ numbers assume group rollouts landing. Conservative read: cap at 300-400 hotels M36.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8317,7 +6837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10679,7 +9199,7 @@
       </c>
       <c r="B46" s="138" t="inlineStr">
         <is>
-          <t>Covers worst case (high cost + low revenue) with CHF 100K share capital. Maximum shareholder commitment.</t>
+          <t>Covers worst case (high cost + low revenue) with CHF 100K share capital. Maximum initial funding envelope.</t>
         </is>
       </c>
       <c r="C46" s="195" t="n"/>
@@ -10702,7 +9222,7 @@
       </c>
       <c r="B48" s="134" t="inlineStr">
         <is>
-          <t>CHF 120K = lean start (CHF 50K share capital, tight buffer). CHF 150K = comfortable (CHF 100K share capital, room for 1 hire). Shareholders decide based on risk appetite.</t>
+          <t>CHF 120K = lean start (CHF 50K share capital, tight buffer). CHF 150K = comfortable (CHF 100K share capital, room for 1 hire). Founding team decides based on risk appetite.</t>
         </is>
       </c>
       <c r="C48" s="127" t="n"/>
@@ -11174,7 +9694,7 @@
     <row r="84" ht="15" customHeight="1" s="125">
       <c r="A84" s="127" t="inlineStr">
         <is>
-          <t>4. Shareholder dividends (optional)</t>
+          <t>4. Profit distribution (optional)</t>
         </is>
       </c>
       <c r="D84" s="152" t="inlineStr">
@@ -11198,29 +9718,29 @@
     <row r="87" ht="15" customHeight="1" s="125">
       <c r="A87" s="152" t="inlineStr">
         <is>
-          <t>DEFAULT: Retain 80-100% of profits for growth in years 1-3. Dividends deferred until growth stabilizes.</t>
+          <t>DEFAULT: Retain 80-100% of profits for growth in years 1-3. Distributions deferred until growth stabilizes.</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="125">
       <c r="A88" s="152" t="inlineStr">
         <is>
-          <t>Retained earnings are a balance-sheet asset of the AG, visible in annual financials, subject to shareholder approval at AGM.</t>
+          <t>Retained earnings stay on the company balance sheet and are visible in annual financials.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" s="125">
       <c r="A89" s="152" t="inlineStr">
         <is>
-          <t>With 3 shareholders and no VC board, dividend distribution is a genuine option — but growth reinvestment is the default.</t>
+          <t>Profit distributions are possible later, but reinvestment is the default while the company is scaling.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A55:E55"/>
+    <mergeCell ref="B41:E41"/>
     <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="B43:E43"/>
@@ -12826,1893 +11346,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
-  </sheetPr>
-  <dimension ref="A1:I88"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="42" customWidth="1" style="124" min="1" max="1"/>
-    <col width="22" customWidth="1" style="124" min="2" max="2"/>
-    <col width="16" customWidth="1" style="124" min="3" max="4"/>
-    <col width="18" customWidth="1" style="124" min="5" max="5"/>
-    <col width="16" customWidth="1" style="124" min="6" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.75" customHeight="1" s="125">
-      <c r="A1" s="126" t="inlineStr">
-        <is>
-          <t>TERCIER AG — Equity Structure &amp; Cap Table</t>
-        </is>
-      </c>
-      <c r="B1" s="127" t="n"/>
-      <c r="C1" s="127" t="n"/>
-      <c r="D1" s="127" t="n"/>
-      <c r="E1" s="127" t="n"/>
-      <c r="F1" s="127" t="n"/>
-      <c r="G1" s="127" t="n"/>
-      <c r="H1" s="127" t="n"/>
-      <c r="I1" s="127" t="n"/>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="125">
-      <c r="A2" s="128" t="inlineStr">
-        <is>
-          <t>All inputs in BLUE. All formulas in BLACK. All cross-sheet links in GREEN. Yellow fill = key assumptions.</t>
-        </is>
-      </c>
-      <c r="H2" s="127" t="n"/>
-      <c r="I2" s="127" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="125">
-      <c r="A3" s="127" t="n"/>
-      <c r="B3" s="127" t="n"/>
-      <c r="C3" s="127" t="n"/>
-      <c r="D3" s="127" t="n"/>
-      <c r="E3" s="127" t="n"/>
-      <c r="F3" s="127" t="n"/>
-      <c r="G3" s="127" t="n"/>
-      <c r="H3" s="127" t="n"/>
-      <c r="I3" s="127" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" s="125">
-      <c r="A4" s="129" t="inlineStr">
-        <is>
-          <t>A. CONTRIBUTION ANALYSIS — WHAT EACH PARTY BRINGS</t>
-        </is>
-      </c>
-      <c r="B4" s="130" t="n"/>
-      <c r="C4" s="130" t="n"/>
-      <c r="D4" s="130" t="n"/>
-      <c r="E4" s="130" t="n"/>
-      <c r="F4" s="130" t="n"/>
-      <c r="G4" s="130" t="n"/>
-      <c r="H4" s="130" t="n"/>
-      <c r="I4" s="130" t="n"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="125">
-      <c r="A5" s="131" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="B5" s="132" t="inlineStr">
-        <is>
-          <t>Guffanti &amp; Corsaro</t>
-        </is>
-      </c>
-      <c r="C5" s="132" t="inlineStr">
-        <is>
-          <t>Marco Di Cesare</t>
-        </is>
-      </c>
-      <c r="D5" s="132" t="inlineStr">
-        <is>
-          <t>Valuation Method</t>
-        </is>
-      </c>
-      <c r="E5" s="133" t="n"/>
-      <c r="F5" s="133" t="n"/>
-      <c r="G5" s="133" t="n"/>
-      <c r="H5" s="133" t="n"/>
-      <c r="I5" s="133" t="n"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1" s="125">
-      <c r="A6" s="134" t="inlineStr">
-        <is>
-          <t>Cash capital (CHF)</t>
-        </is>
-      </c>
-      <c r="B6" s="134" t="inlineStr">
-        <is>
-          <t>CHF 100-200K</t>
-        </is>
-      </c>
-      <c r="C6" s="134" t="inlineStr">
-        <is>
-          <t>CHF 0</t>
-        </is>
-      </c>
-      <c r="D6" s="136" t="inlineStr">
-        <is>
-          <t>Face value</t>
-        </is>
-      </c>
-      <c r="E6" s="127" t="n"/>
-      <c r="F6" s="127" t="n"/>
-      <c r="G6" s="127" t="n"/>
-      <c r="H6" s="127" t="n"/>
-      <c r="I6" s="127" t="n"/>
-    </row>
-    <row r="7" ht="19.5" customHeight="1" s="125">
-      <c r="A7" s="138" t="inlineStr">
-        <is>
-          <t>Original idea / concept</t>
-        </is>
-      </c>
-      <c r="B7" s="138" t="inlineStr">
-        <is>
-          <t>Yes — conceived the business</t>
-        </is>
-      </c>
-      <c r="C7" s="138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D7" s="136" t="inlineStr">
-        <is>
-          <t>Slicing Pie: 2x non-cash multiplier</t>
-        </is>
-      </c>
-      <c r="E7" s="127" t="n"/>
-      <c r="F7" s="127" t="n"/>
-      <c r="G7" s="127" t="n"/>
-      <c r="H7" s="127" t="n"/>
-      <c r="I7" s="127" t="n"/>
-    </row>
-    <row r="8" ht="19.5" customHeight="1" s="125">
-      <c r="A8" s="134" t="inlineStr">
-        <is>
-          <t>First prototype / MVP</t>
-        </is>
-      </c>
-      <c r="B8" s="134" t="inlineStr">
-        <is>
-          <t>Funded development</t>
-        </is>
-      </c>
-      <c r="C8" s="134" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D8" s="136" t="inlineStr">
-        <is>
-          <t>Included in cash valuation</t>
-        </is>
-      </c>
-      <c r="E8" s="127" t="n"/>
-      <c r="F8" s="127" t="n"/>
-      <c r="G8" s="127" t="n"/>
-      <c r="H8" s="127" t="n"/>
-      <c r="I8" s="127" t="n"/>
-    </row>
-    <row r="9" ht="19.5" customHeight="1" s="125">
-      <c r="A9" s="138" t="inlineStr">
-        <is>
-          <t>Pilot client</t>
-        </is>
-      </c>
-      <c r="B9" s="138" t="inlineStr">
-        <is>
-          <t>1 hotel (relationship)</t>
-        </is>
-      </c>
-      <c r="C9" s="138" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D9" s="136" t="inlineStr">
-        <is>
-          <t>De-risks product; ~EUR 15-30K LTV</t>
-        </is>
-      </c>
-      <c r="E9" s="127" t="n"/>
-      <c r="F9" s="127" t="n"/>
-      <c r="G9" s="127" t="n"/>
-      <c r="H9" s="127" t="n"/>
-      <c r="I9" s="127" t="n"/>
-    </row>
-    <row r="10" ht="19.5" customHeight="1" s="125">
-      <c r="A10" s="134" t="inlineStr">
-        <is>
-          <t>Distribution network</t>
-        </is>
-      </c>
-      <c r="B10" s="134" t="inlineStr">
-        <is>
-          <t>Hospitality industry contacts</t>
-        </is>
-      </c>
-      <c r="C10" s="134" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D10" s="136" t="inlineStr">
-        <is>
-          <t>Hard to value; reduces CAC by 50-80%</t>
-        </is>
-      </c>
-      <c r="E10" s="127" t="n"/>
-      <c r="F10" s="127" t="n"/>
-      <c r="G10" s="127" t="n"/>
-      <c r="H10" s="127" t="n"/>
-      <c r="I10" s="127" t="n"/>
-    </row>
-    <row r="11" ht="19.5" customHeight="1" s="125">
-      <c r="A11" s="138" t="inlineStr">
-        <is>
-          <t>Daily operations</t>
-        </is>
-      </c>
-      <c r="B11" s="138" t="inlineStr">
-        <is>
-          <t>None — zero hours/day</t>
-        </is>
-      </c>
-      <c r="C11" s="138" t="inlineStr">
-        <is>
-          <t>100% — sole operator</t>
-        </is>
-      </c>
-      <c r="D11" s="136" t="inlineStr">
-        <is>
-          <t>Sweat equity: EUR 32-47K/yr foregone</t>
-        </is>
-      </c>
-      <c r="E11" s="127" t="n"/>
-      <c r="F11" s="127" t="n"/>
-      <c r="G11" s="127" t="n"/>
-      <c r="H11" s="127" t="n"/>
-      <c r="I11" s="127" t="n"/>
-    </row>
-    <row r="12" ht="19.5" customHeight="1" s="125">
-      <c r="A12" s="134" t="inlineStr">
-        <is>
-          <t>Engineering / product</t>
-        </is>
-      </c>
-      <c r="B12" s="134" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C12" s="134" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D12" s="136" t="inlineStr">
-        <is>
-          <t>Market rate: EUR 80-120K/yr</t>
-        </is>
-      </c>
-      <c r="E12" s="127" t="n"/>
-      <c r="F12" s="127" t="n"/>
-      <c r="G12" s="127" t="n"/>
-      <c r="H12" s="127" t="n"/>
-      <c r="I12" s="127" t="n"/>
-    </row>
-    <row r="13" ht="19.5" customHeight="1" s="125">
-      <c r="A13" s="138" t="inlineStr">
-        <is>
-          <t>Customer success / onboarding</t>
-        </is>
-      </c>
-      <c r="B13" s="138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C13" s="138" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D13" s="136" t="inlineStr">
-        <is>
-          <t>Market rate: EUR 50-70K/yr</t>
-        </is>
-      </c>
-      <c r="E13" s="127" t="n"/>
-      <c r="F13" s="127" t="n"/>
-      <c r="G13" s="127" t="n"/>
-      <c r="H13" s="127" t="n"/>
-      <c r="I13" s="127" t="n"/>
-    </row>
-    <row r="14" ht="19.5" customHeight="1" s="125">
-      <c r="A14" s="134" t="inlineStr">
-        <is>
-          <t>Company formation work</t>
-        </is>
-      </c>
-      <c r="B14" s="134" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="C14" s="134" t="inlineStr">
-        <is>
-          <t>Name, domain, Swiss hotel dataset</t>
-        </is>
-      </c>
-      <c r="D14" s="136" t="inlineStr">
-        <is>
-          <t>~200 hrs × EUR 60/hr = EUR 12K</t>
-        </is>
-      </c>
-      <c r="E14" s="127" t="n"/>
-      <c r="F14" s="127" t="n"/>
-      <c r="G14" s="127" t="n"/>
-      <c r="H14" s="127" t="n"/>
-      <c r="I14" s="127" t="n"/>
-    </row>
-    <row r="15" ht="19.5" customHeight="1" s="125">
-      <c r="A15" s="138" t="inlineStr">
-        <is>
-          <t>Below-market salary sacrifice</t>
-        </is>
-      </c>
-      <c r="B15" s="138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C15" s="138" t="inlineStr">
-        <is>
-          <t>CHF 48K vs EUR 85-100K market</t>
-        </is>
-      </c>
-      <c r="D15" s="136" t="inlineStr">
-        <is>
-          <t>EUR 32-47K/yr × 2 yr = EUR 64-94K</t>
-        </is>
-      </c>
-      <c r="E15" s="127" t="n"/>
-      <c r="F15" s="127" t="n"/>
-      <c r="G15" s="127" t="n"/>
-      <c r="H15" s="127" t="n"/>
-      <c r="I15" s="127" t="n"/>
-    </row>
-    <row r="16" ht="19.5" customHeight="1" s="125">
-      <c r="A16" s="134" t="inlineStr">
-        <is>
-          <t>Ongoing time commitment</t>
-        </is>
-      </c>
-      <c r="B16" s="134" t="inlineStr">
-        <is>
-          <t>2-5 hrs/month (intros, board)</t>
-        </is>
-      </c>
-      <c r="C16" s="134" t="inlineStr">
-        <is>
-          <t>200+ hrs/month (everything)</t>
-        </is>
-      </c>
-      <c r="D16" s="136" t="inlineStr">
-        <is>
-          <t>Ratio: 1:40 to 1:100</t>
-        </is>
-      </c>
-      <c r="E16" s="127" t="n"/>
-      <c r="F16" s="127" t="n"/>
-      <c r="G16" s="127" t="n"/>
-      <c r="H16" s="127" t="n"/>
-      <c r="I16" s="127" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="125">
-      <c r="A17" s="127" t="n"/>
-      <c r="B17" s="127" t="n"/>
-      <c r="C17" s="127" t="n"/>
-      <c r="D17" s="127" t="n"/>
-      <c r="E17" s="127" t="n"/>
-      <c r="F17" s="127" t="n"/>
-      <c r="G17" s="127" t="n"/>
-      <c r="H17" s="127" t="n"/>
-      <c r="I17" s="127" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" s="125">
-      <c r="A18" s="129" t="inlineStr">
-        <is>
-          <t>B. SWEAT EQUITY CALCULATION (Marco Di Cesare)</t>
-        </is>
-      </c>
-      <c r="B18" s="130" t="n"/>
-      <c r="C18" s="130" t="n"/>
-      <c r="D18" s="130" t="n"/>
-      <c r="E18" s="130" t="n"/>
-      <c r="F18" s="130" t="n"/>
-      <c r="G18" s="130" t="n"/>
-      <c r="H18" s="130" t="n"/>
-      <c r="I18" s="130" t="n"/>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" s="125">
-      <c r="A19" s="131" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B19" s="132" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C19" s="132" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="D19" s="132" t="inlineStr">
-        <is>
-          <t>Derivation</t>
-        </is>
-      </c>
-      <c r="E19" s="132" t="inlineStr">
-        <is>
-          <t>Source URL</t>
-        </is>
-      </c>
-      <c r="F19" s="133" t="n"/>
-      <c r="G19" s="133" t="n"/>
-      <c r="H19" s="133" t="n"/>
-      <c r="I19" s="133" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1" s="125">
-      <c r="A20" s="134" t="inlineStr">
-        <is>
-          <t>European founder median salary</t>
-        </is>
-      </c>
-      <c r="B20" s="143" t="n">
-        <v>92500</v>
-      </c>
-      <c r="C20" s="134" t="inlineStr">
-        <is>
-          <t>EUR/yr</t>
-        </is>
-      </c>
-      <c r="D20" s="136" t="inlineStr">
-        <is>
-          <t>Creandum 2025: EUR 85-100K median, midpoint</t>
-        </is>
-      </c>
-      <c r="E20" s="204" t="inlineStr">
-        <is>
-          <t>https://www.creandum.com/reports/founder-compensation-2025</t>
-        </is>
-      </c>
-      <c r="F20" s="127" t="n"/>
-      <c r="G20" s="127" t="n"/>
-      <c r="H20" s="127" t="n"/>
-      <c r="I20" s="127" t="n"/>
-    </row>
-    <row r="21" ht="19.5" customHeight="1" s="125">
-      <c r="A21" s="138" t="inlineStr">
-        <is>
-          <t>Actual salary (CHF 48K)</t>
-        </is>
-      </c>
-      <c r="B21" s="144" t="n">
-        <v>66667</v>
-      </c>
-      <c r="C21" s="138" t="inlineStr">
-        <is>
-          <t>EUR/yr</t>
-        </is>
-      </c>
-      <c r="D21" s="136" t="inlineStr">
-        <is>
-          <t>CHF 48K / 0.91 FX</t>
-        </is>
-      </c>
-      <c r="E21" s="127" t="n"/>
-      <c r="F21" s="127" t="n"/>
-      <c r="G21" s="127" t="n"/>
-      <c r="H21" s="127" t="n"/>
-      <c r="I21" s="127" t="n"/>
-    </row>
-    <row r="22" ht="19.5" customHeight="1" s="125">
-      <c r="A22" s="134" t="inlineStr">
-        <is>
-          <t>Annual salary foregone</t>
-        </is>
-      </c>
-      <c r="B22" s="143" t="n">
-        <v>25833</v>
-      </c>
-      <c r="C22" s="134" t="inlineStr">
-        <is>
-          <t>EUR/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="136" t="inlineStr">
-        <is>
-          <t>Market rate - actual salary</t>
-        </is>
-      </c>
-      <c r="E22" s="127" t="n"/>
-      <c r="F22" s="127" t="n"/>
-      <c r="G22" s="127" t="n"/>
-      <c r="H22" s="127" t="n"/>
-      <c r="I22" s="127" t="n"/>
-    </row>
-    <row r="23" ht="19.5" customHeight="1" s="125">
-      <c r="A23" s="138" t="inlineStr">
-        <is>
-          <t>Pre-formation work (dataset, domain, name)</t>
-        </is>
-      </c>
-      <c r="B23" s="144" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C23" s="138" t="inlineStr">
-        <is>
-          <t>EUR one-time</t>
-        </is>
-      </c>
-      <c r="D23" s="136" t="inlineStr">
-        <is>
-          <t>~200 hrs × EUR 60/hr</t>
-        </is>
-      </c>
-      <c r="E23" s="127" t="n"/>
-      <c r="F23" s="127" t="n"/>
-      <c r="G23" s="127" t="n"/>
-      <c r="H23" s="127" t="n"/>
-      <c r="I23" s="127" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1" s="125">
-      <c r="A24" s="134" t="inlineStr">
-        <is>
-          <t>Sweat equity over 24 months</t>
-        </is>
-      </c>
-      <c r="B24" s="143" t="n">
-        <v>73666</v>
-      </c>
-      <c r="C24" s="134" t="inlineStr">
-        <is>
-          <t>EUR total</t>
-        </is>
-      </c>
-      <c r="D24" s="136" t="inlineStr">
-        <is>
-          <t>(25,833 × 2) + 12,000 + 10,000 opportunity cost</t>
-        </is>
-      </c>
-      <c r="E24" s="127" t="n"/>
-      <c r="F24" s="127" t="n"/>
-      <c r="G24" s="127" t="n"/>
-      <c r="H24" s="127" t="n"/>
-      <c r="I24" s="127" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="125">
-      <c r="A25" s="127" t="n"/>
-      <c r="B25" s="127" t="n"/>
-      <c r="C25" s="127" t="n"/>
-      <c r="D25" s="127" t="n"/>
-      <c r="E25" s="127" t="n"/>
-      <c r="F25" s="127" t="n"/>
-      <c r="G25" s="127" t="n"/>
-      <c r="H25" s="127" t="n"/>
-      <c r="I25" s="127" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" s="125">
-      <c r="A26" s="129" t="inlineStr">
-        <is>
-          <t>C. SLICING PIE VALUATION (Dynamic Equity Framework)</t>
-        </is>
-      </c>
-      <c r="B26" s="130" t="n"/>
-      <c r="C26" s="130" t="n"/>
-      <c r="D26" s="130" t="n"/>
-      <c r="E26" s="130" t="n"/>
-      <c r="F26" s="130" t="n"/>
-      <c r="G26" s="130" t="n"/>
-      <c r="H26" s="130" t="n"/>
-      <c r="I26" s="130" t="n"/>
-    </row>
-    <row r="27" ht="19.5" customHeight="1" s="125">
-      <c r="A27" s="134" t="inlineStr">
-        <is>
-          <t>Source:</t>
-        </is>
-      </c>
-      <c r="B27" s="204" t="inlineStr">
-        <is>
-          <t>https://slicingpie.com</t>
-        </is>
-      </c>
-      <c r="C27" s="127" t="n"/>
-      <c r="D27" s="127" t="n"/>
-      <c r="E27" s="127" t="n"/>
-      <c r="F27" s="127" t="n"/>
-      <c r="G27" s="127" t="n"/>
-      <c r="H27" s="127" t="n"/>
-      <c r="I27" s="127" t="n"/>
-    </row>
-    <row r="28" ht="21.75" customHeight="1" s="125">
-      <c r="A28" s="131" t="inlineStr">
-        <is>
-          <t>Contributor</t>
-        </is>
-      </c>
-      <c r="B28" s="132" t="inlineStr">
-        <is>
-          <t>At-Risk Value (EUR)</t>
-        </is>
-      </c>
-      <c r="C28" s="132" t="inlineStr">
-        <is>
-          <t>Multiplier</t>
-        </is>
-      </c>
-      <c r="D28" s="132" t="inlineStr">
-        <is>
-          <t>Slices</t>
-        </is>
-      </c>
-      <c r="E28" s="132" t="inlineStr">
-        <is>
-          <t>% of Total</t>
-        </is>
-      </c>
-      <c r="F28" s="133" t="n"/>
-      <c r="G28" s="133" t="n"/>
-      <c r="H28" s="133" t="n"/>
-      <c r="I28" s="133" t="n"/>
-    </row>
-    <row r="29" ht="19.5" customHeight="1" s="125">
-      <c r="A29" s="134" t="inlineStr">
-        <is>
-          <t>G&amp;C: Cash capital (initial seed range)</t>
-        </is>
-      </c>
-      <c r="B29" s="143" t="n">
-        <v>164835</v>
-      </c>
-      <c r="C29" s="136" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="143" t="inlineStr">
-        <is>
-          <t>Corrected seed anchor at CHF 150K / 0.91 FX</t>
-        </is>
-      </c>
-      <c r="E29" s="127" t="n"/>
-      <c r="F29" s="127" t="n"/>
-      <c r="G29" s="127" t="n"/>
-      <c r="H29" s="127" t="n"/>
-      <c r="I29" s="127" t="n"/>
-    </row>
-    <row r="30" ht="19.5" customHeight="1" s="125">
-      <c r="A30" s="138" t="inlineStr">
-        <is>
-          <t>G&amp;C: Idea + network + pilot client</t>
-        </is>
-      </c>
-      <c r="B30" s="144" t="n">
-        <v>80000</v>
-      </c>
-      <c r="C30" s="136" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="144">
-        <f>B30*C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="127" t="n"/>
-      <c r="F30" s="127" t="n"/>
-      <c r="G30" s="127" t="n"/>
-      <c r="H30" s="127" t="n"/>
-      <c r="I30" s="127" t="n"/>
-    </row>
-    <row r="31" ht="19.5" customHeight="1" s="125">
-      <c r="A31" s="134" t="inlineStr">
-        <is>
-          <t>MDC: Sweat equity (24 months)</t>
-        </is>
-      </c>
-      <c r="B31" s="143" t="n">
-        <v>73666</v>
-      </c>
-      <c r="C31" s="136" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="143">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="127" t="n"/>
-      <c r="F31" s="127" t="n"/>
-      <c r="G31" s="127" t="n"/>
-      <c r="H31" s="127" t="n"/>
-      <c r="I31" s="127" t="n"/>
-    </row>
-    <row r="32" ht="19.5" customHeight="1" s="125">
-      <c r="A32" s="138" t="inlineStr">
-        <is>
-          <t>MDC: Ongoing execution value (24 mo)</t>
-        </is>
-      </c>
-      <c r="B32" s="144" t="n">
-        <v>200000</v>
-      </c>
-      <c r="C32" s="136" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="144">
-        <f>B32*C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="127" t="n"/>
-      <c r="F32" s="127" t="n"/>
-      <c r="G32" s="127" t="n"/>
-      <c r="H32" s="127" t="n"/>
-      <c r="I32" s="127" t="n"/>
-    </row>
-    <row r="33" ht="19.5" customHeight="1" s="125">
-      <c r="A33" s="194" t="inlineStr">
-        <is>
-          <t>TOTAL SLICES</t>
-        </is>
-      </c>
-      <c r="B33" s="127" t="n"/>
-      <c r="C33" s="127" t="n"/>
-      <c r="D33" s="143">
-        <f>SUM(D29:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="127" t="n"/>
-      <c r="F33" s="127" t="n"/>
-      <c r="G33" s="127" t="n"/>
-      <c r="H33" s="127" t="n"/>
-      <c r="I33" s="127" t="n"/>
-    </row>
-    <row r="34" ht="19.5" customHeight="1" s="125">
-      <c r="A34" s="194" t="inlineStr">
-        <is>
-          <t>G&amp;C share</t>
-        </is>
-      </c>
-      <c r="B34" s="127" t="n"/>
-      <c r="C34" s="127" t="n"/>
-      <c r="D34" s="127" t="n"/>
-      <c r="E34" s="145">
-        <f>(D29+D30)/D33</f>
-        <v/>
-      </c>
-      <c r="F34" s="127" t="n"/>
-      <c r="G34" s="127" t="n"/>
-      <c r="H34" s="127" t="n"/>
-      <c r="I34" s="127" t="n"/>
-    </row>
-    <row r="35" ht="19.5" customHeight="1" s="125">
-      <c r="A35" s="194" t="inlineStr">
-        <is>
-          <t>MDC share</t>
-        </is>
-      </c>
-      <c r="B35" s="127" t="n"/>
-      <c r="C35" s="127" t="n"/>
-      <c r="D35" s="127" t="n"/>
-      <c r="E35" s="179">
-        <f>(D31+D32)/D33</f>
-        <v/>
-      </c>
-      <c r="F35" s="127" t="n"/>
-      <c r="G35" s="127" t="n"/>
-      <c r="H35" s="127" t="n"/>
-      <c r="I35" s="127" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="125">
-      <c r="A36" s="127" t="n"/>
-      <c r="B36" s="127" t="n"/>
-      <c r="C36" s="127" t="n"/>
-      <c r="D36" s="127" t="n"/>
-      <c r="E36" s="127" t="n"/>
-      <c r="F36" s="127" t="n"/>
-      <c r="G36" s="127" t="n"/>
-      <c r="H36" s="127" t="n"/>
-      <c r="I36" s="127" t="n"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" s="125">
-      <c r="A37" s="129" t="inlineStr">
-        <is>
-          <t>D. RECOMMENDED EQUITY SPLITS (3 SCENARIOS)</t>
-        </is>
-      </c>
-      <c r="B37" s="130" t="n"/>
-      <c r="C37" s="130" t="n"/>
-      <c r="D37" s="130" t="n"/>
-      <c r="E37" s="130" t="n"/>
-      <c r="F37" s="130" t="n"/>
-      <c r="G37" s="130" t="n"/>
-      <c r="H37" s="130" t="n"/>
-      <c r="I37" s="130" t="n"/>
-    </row>
-    <row r="38" ht="21.75" customHeight="1" s="125">
-      <c r="A38" s="131" t="inlineStr">
-        <is>
-          <t>Party</t>
-        </is>
-      </c>
-      <c r="B38" s="132" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="C38" s="132" t="inlineStr">
-        <is>
-          <t>Balanced (Recommended)</t>
-        </is>
-      </c>
-      <c r="D38" s="132" t="inlineStr">
-        <is>
-          <t>Founder-Friendly</t>
-        </is>
-      </c>
-      <c r="E38" s="133" t="n"/>
-      <c r="F38" s="133" t="n"/>
-      <c r="G38" s="133" t="n"/>
-      <c r="H38" s="133" t="n"/>
-      <c r="I38" s="133" t="n"/>
-    </row>
-    <row r="39" ht="19.5" customHeight="1" s="125">
-      <c r="A39" s="134" t="inlineStr">
-        <is>
-          <t>Amedeo Guffanti</t>
-        </is>
-      </c>
-      <c r="B39" s="179" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="C39" s="185" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D39" s="179" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E39" s="127" t="n"/>
-      <c r="F39" s="127" t="n"/>
-      <c r="G39" s="127" t="n"/>
-      <c r="H39" s="127" t="n"/>
-      <c r="I39" s="127" t="n"/>
-    </row>
-    <row r="40" ht="19.5" customHeight="1" s="125">
-      <c r="A40" s="138" t="inlineStr">
-        <is>
-          <t>Marco Corsaro</t>
-        </is>
-      </c>
-      <c r="B40" s="145" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="C40" s="185" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D40" s="145" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E40" s="127" t="n"/>
-      <c r="F40" s="127" t="n"/>
-      <c r="G40" s="127" t="n"/>
-      <c r="H40" s="127" t="n"/>
-      <c r="I40" s="127" t="n"/>
-    </row>
-    <row r="41" ht="19.5" customHeight="1" s="125">
-      <c r="A41" s="134" t="inlineStr">
-        <is>
-          <t>Marco Di Cesare (operator)</t>
-        </is>
-      </c>
-      <c r="B41" s="179" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="C41" s="185" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D41" s="179" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E41" s="127" t="n"/>
-      <c r="F41" s="127" t="n"/>
-      <c r="G41" s="127" t="n"/>
-      <c r="H41" s="127" t="n"/>
-      <c r="I41" s="127" t="n"/>
-    </row>
-    <row r="42" ht="19.5" customHeight="1" s="125">
-      <c r="A42" s="136" t="inlineStr">
-        <is>
-          <t>ESOP pool (future hires)</t>
-        </is>
-      </c>
-      <c r="B42" s="205" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C42" s="205" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D42" s="205" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E42" s="127" t="n"/>
-      <c r="F42" s="127" t="n"/>
-      <c r="G42" s="127" t="n"/>
-      <c r="H42" s="127" t="n"/>
-      <c r="I42" s="127" t="n"/>
-    </row>
-    <row r="43" ht="19.5" customHeight="1" s="125">
-      <c r="A43" s="194" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B43" s="179">
-        <f>SUM(B39:B42)</f>
-        <v/>
-      </c>
-      <c r="C43" s="179">
-        <f>SUM(C39:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="179">
-        <f>SUM(D39:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="127" t="n"/>
-      <c r="F43" s="127" t="n"/>
-      <c r="G43" s="127" t="n"/>
-      <c r="H43" s="127" t="n"/>
-      <c r="I43" s="127" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="125">
-      <c r="A44" s="127" t="n"/>
-      <c r="B44" s="127" t="n"/>
-      <c r="F44" s="127" t="n"/>
-      <c r="G44" s="127" t="n"/>
-      <c r="H44" s="127" t="n"/>
-      <c r="I44" s="127" t="n"/>
-    </row>
-    <row r="45" ht="19.5" customHeight="1" s="125">
-      <c r="A45" s="134" t="inlineStr">
-        <is>
-          <t>Conservative (45/45/10):</t>
-        </is>
-      </c>
-      <c r="B45" s="134" t="inlineStr">
-        <is>
-          <t>Capital + idea + network weighted equally to full-time execution. Standard for investor-heavy seed. May undervalue Marco's daily work over time.</t>
-        </is>
-      </c>
-      <c r="C45" s="195" t="n"/>
-      <c r="D45" s="195" t="n"/>
-      <c r="E45" s="195" t="n"/>
-      <c r="F45" s="127" t="n"/>
-      <c r="G45" s="127" t="n"/>
-      <c r="H45" s="127" t="n"/>
-      <c r="I45" s="127" t="n"/>
-    </row>
-    <row r="46" ht="19.5" customHeight="1" s="125">
-      <c r="A46" s="138" t="inlineStr">
-        <is>
-          <t>Balanced (40/50/10):</t>
-        </is>
-      </c>
-      <c r="B46" s="138" t="inlineStr">
-        <is>
-          <t>Reflects that in B2B SaaS, the operator creates 80%+ of value post-funding. Aligns with Carta data: 76% of co-founder teams now use unequal splits. Leaves clean cap table for Series A.</t>
-        </is>
-      </c>
-      <c r="C46" s="195" t="n"/>
-      <c r="D46" s="195" t="n"/>
-      <c r="E46" s="195" t="n"/>
-      <c r="F46" s="127" t="n"/>
-      <c r="G46" s="127" t="n"/>
-      <c r="H46" s="127" t="n"/>
-      <c r="I46" s="127" t="n"/>
-    </row>
-    <row r="47" ht="19.5" customHeight="1" s="125">
-      <c r="A47" s="134" t="inlineStr">
-        <is>
-          <t>Founder-Friendly (32/56/12):</t>
-        </is>
-      </c>
-      <c r="B47" s="134" t="inlineStr">
-        <is>
-          <t>Pure Slicing Pie output. Maximizes operator upside. Works if investors are truly passive and no institutional fundraising planned.</t>
-        </is>
-      </c>
-      <c r="C47" s="127" t="n"/>
-      <c r="D47" s="127" t="n"/>
-      <c r="E47" s="127" t="n"/>
-      <c r="F47" s="127" t="n"/>
-      <c r="G47" s="127" t="n"/>
-      <c r="H47" s="127" t="n"/>
-      <c r="I47" s="127" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="125">
-      <c r="A48" s="127" t="n"/>
-      <c r="B48" s="127" t="n"/>
-      <c r="C48" s="127" t="n"/>
-      <c r="D48" s="127" t="n"/>
-      <c r="E48" s="127" t="n"/>
-      <c r="F48" s="127" t="n"/>
-      <c r="G48" s="127" t="n"/>
-      <c r="H48" s="127" t="n"/>
-      <c r="I48" s="127" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="125">
-      <c r="A49" s="127" t="n"/>
-      <c r="B49" s="127" t="n"/>
-      <c r="C49" s="127" t="n"/>
-      <c r="D49" s="127" t="n"/>
-      <c r="E49" s="127" t="n"/>
-      <c r="F49" s="127" t="n"/>
-      <c r="G49" s="127" t="n"/>
-      <c r="H49" s="127" t="n"/>
-      <c r="I49" s="127" t="n"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" s="125">
-      <c r="A50" s="129" t="inlineStr">
-        <is>
-          <t>E. VESTING SCHEDULE — MARCO DI CESARE (50% grant, Balanced scenario)</t>
-        </is>
-      </c>
-      <c r="B50" s="130" t="n"/>
-      <c r="C50" s="130" t="n"/>
-      <c r="D50" s="130" t="n"/>
-      <c r="E50" s="130" t="n"/>
-      <c r="F50" s="130" t="n"/>
-      <c r="G50" s="130" t="n"/>
-      <c r="H50" s="130" t="n"/>
-      <c r="I50" s="130" t="n"/>
-    </row>
-    <row r="51" ht="21.75" customHeight="1" s="125">
-      <c r="A51" s="131" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B51" s="132" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-      <c r="C51" s="132" t="inlineStr">
-        <is>
-          <t>Shares Vesting</t>
-        </is>
-      </c>
-      <c r="D51" s="132" t="inlineStr">
-        <is>
-          <t>Cumulative Vested</t>
-        </is>
-      </c>
-      <c r="E51" s="132" t="inlineStr">
-        <is>
-          <t>% of Company</t>
-        </is>
-      </c>
-      <c r="F51" s="133" t="n"/>
-      <c r="G51" s="133" t="n"/>
-      <c r="H51" s="133" t="n"/>
-      <c r="I51" s="133" t="n"/>
-    </row>
-    <row r="52" ht="19.5" customHeight="1" s="125">
-      <c r="A52" s="148" t="n">
-        <v>0</v>
-      </c>
-      <c r="B52" s="134" t="inlineStr">
-        <is>
-          <t>Grant date — 500 shares restricted</t>
-        </is>
-      </c>
-      <c r="C52" s="148" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="148" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="134" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="F52" s="127" t="n"/>
-      <c r="G52" s="127" t="n"/>
-      <c r="H52" s="127" t="n"/>
-      <c r="I52" s="127" t="n"/>
-    </row>
-    <row r="53" ht="19.5" customHeight="1" s="125">
-      <c r="A53" s="206" t="n">
-        <v>12</v>
-      </c>
-      <c r="B53" s="180" t="inlineStr">
-        <is>
-          <t>1-year cliff — 25% vests</t>
-        </is>
-      </c>
-      <c r="C53" s="206" t="n">
-        <v>125</v>
-      </c>
-      <c r="D53" s="206" t="n">
-        <v>125</v>
-      </c>
-      <c r="E53" s="180" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="F53" s="127" t="n"/>
-      <c r="G53" s="127" t="n"/>
-      <c r="H53" s="127" t="n"/>
-      <c r="I53" s="127" t="n"/>
-    </row>
-    <row r="54" ht="19.5" customHeight="1" s="125">
-      <c r="A54" s="148" t="n">
-        <v>24</v>
-      </c>
-      <c r="B54" s="134" t="inlineStr">
-        <is>
-          <t>Year 2 complete (monthly vesting)</t>
-        </is>
-      </c>
-      <c r="C54" s="148" t="n">
-        <v>125</v>
-      </c>
-      <c r="D54" s="148" t="n">
-        <v>250</v>
-      </c>
-      <c r="E54" s="134" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="F54" s="127" t="n"/>
-      <c r="G54" s="127" t="n"/>
-      <c r="H54" s="127" t="n"/>
-      <c r="I54" s="127" t="n"/>
-    </row>
-    <row r="55" ht="19.5" customHeight="1" s="125">
-      <c r="A55" s="187" t="n">
-        <v>36</v>
-      </c>
-      <c r="B55" s="138" t="inlineStr">
-        <is>
-          <t>Year 3 complete</t>
-        </is>
-      </c>
-      <c r="C55" s="187" t="n">
-        <v>125</v>
-      </c>
-      <c r="D55" s="187" t="n">
-        <v>375</v>
-      </c>
-      <c r="E55" s="138" t="inlineStr">
-        <is>
-          <t>37.5%</t>
-        </is>
-      </c>
-      <c r="F55" s="127" t="n"/>
-      <c r="G55" s="127" t="n"/>
-      <c r="H55" s="127" t="n"/>
-      <c r="I55" s="127" t="n"/>
-    </row>
-    <row r="56" ht="19.5" customHeight="1" s="125">
-      <c r="A56" s="183" t="n">
-        <v>48</v>
-      </c>
-      <c r="B56" s="183" t="inlineStr">
-        <is>
-          <t>Year 4 — fully vested</t>
-        </is>
-      </c>
-      <c r="C56" s="183" t="n">
-        <v>125</v>
-      </c>
-      <c r="D56" s="183" t="n">
-        <v>500</v>
-      </c>
-      <c r="E56" s="183" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F56" s="127" t="n"/>
-      <c r="G56" s="127" t="n"/>
-      <c r="H56" s="127" t="n"/>
-      <c r="I56" s="127" t="n"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="125">
-      <c r="A57" s="127" t="n"/>
-      <c r="B57" s="127" t="n"/>
-      <c r="C57" s="127" t="n"/>
-      <c r="D57" s="127" t="n"/>
-      <c r="E57" s="127" t="n"/>
-      <c r="F57" s="127" t="n"/>
-      <c r="G57" s="127" t="n"/>
-      <c r="H57" s="127" t="n"/>
-      <c r="I57" s="127" t="n"/>
-    </row>
-    <row r="58" ht="19.5" customHeight="1" s="125">
-      <c r="A58" s="134" t="inlineStr">
-        <is>
-          <t>Monthly vesting after cliff:</t>
-        </is>
-      </c>
-      <c r="B58" s="134" t="inlineStr">
-        <is>
-          <t>~10.4 shares/month (1/48th of 500)</t>
-        </is>
-      </c>
-      <c r="C58" s="127" t="n"/>
-      <c r="D58" s="127" t="n"/>
-      <c r="E58" s="127" t="n"/>
-      <c r="F58" s="127" t="n"/>
-      <c r="G58" s="127" t="n"/>
-      <c r="H58" s="127" t="n"/>
-      <c r="I58" s="127" t="n"/>
-    </row>
-    <row r="59" ht="19.5" customHeight="1" s="125">
-      <c r="A59" s="138" t="inlineStr">
-        <is>
-          <t>If Marco leaves at month 18:</t>
-        </is>
-      </c>
-      <c r="B59" s="138" t="inlineStr">
-        <is>
-          <t>Keeps 187.5 shares = 18.75% of company. Unvested 312.5 shares return to pool.</t>
-        </is>
-      </c>
-      <c r="C59" s="127" t="n"/>
-      <c r="D59" s="127" t="n"/>
-      <c r="E59" s="127" t="n"/>
-      <c r="F59" s="127" t="n"/>
-      <c r="G59" s="127" t="n"/>
-      <c r="H59" s="127" t="n"/>
-      <c r="I59" s="127" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="125">
-      <c r="A60" s="127" t="n"/>
-      <c r="B60" s="127" t="n"/>
-      <c r="C60" s="127" t="n"/>
-      <c r="D60" s="127" t="n"/>
-      <c r="E60" s="127" t="n"/>
-      <c r="F60" s="127" t="n"/>
-      <c r="G60" s="127" t="n"/>
-      <c r="H60" s="127" t="n"/>
-      <c r="I60" s="127" t="n"/>
-    </row>
-    <row r="61" ht="24" customHeight="1" s="125">
-      <c r="A61" s="129" t="inlineStr">
-        <is>
-          <t>F. MILESTONE ACCELERATION (Optional — on top of time-based vesting)</t>
-        </is>
-      </c>
-      <c r="B61" s="130" t="n"/>
-      <c r="C61" s="130" t="n"/>
-      <c r="D61" s="130" t="n"/>
-      <c r="E61" s="130" t="n"/>
-      <c r="F61" s="130" t="n"/>
-      <c r="G61" s="130" t="n"/>
-      <c r="H61" s="130" t="n"/>
-      <c r="I61" s="130" t="n"/>
-    </row>
-    <row r="62" ht="21.75" customHeight="1" s="125">
-      <c r="A62" s="131" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="B62" s="132" t="inlineStr">
-        <is>
-          <t>MDC Acceleration</t>
-        </is>
-      </c>
-      <c r="C62" s="132" t="inlineStr">
-        <is>
-          <t>G&amp;C Bonus</t>
-        </is>
-      </c>
-      <c r="D62" s="132" t="inlineStr">
-        <is>
-          <t>Rationale</t>
-        </is>
-      </c>
-      <c r="E62" s="133" t="n"/>
-      <c r="F62" s="133" t="n"/>
-      <c r="G62" s="133" t="n"/>
-      <c r="H62" s="133" t="n"/>
-      <c r="I62" s="133" t="n"/>
-    </row>
-    <row r="63" ht="19.5" customHeight="1" s="125">
-      <c r="A63" s="134" t="inlineStr">
-        <is>
-          <t>First 5 paying hotels</t>
-        </is>
-      </c>
-      <c r="B63" s="183" t="inlineStr">
-        <is>
-          <t>+2%</t>
-        </is>
-      </c>
-      <c r="C63" s="134" t="inlineStr">
-        <is>
-          <t>+1%</t>
-        </is>
-      </c>
-      <c r="D63" s="136" t="inlineStr">
-        <is>
-          <t>Product-market fit validated</t>
-        </is>
-      </c>
-      <c r="E63" s="127" t="n"/>
-      <c r="F63" s="127" t="n"/>
-      <c r="G63" s="127" t="n"/>
-      <c r="H63" s="127" t="n"/>
-      <c r="I63" s="127" t="n"/>
-    </row>
-    <row r="64" ht="19.5" customHeight="1" s="125">
-      <c r="A64" s="138" t="inlineStr">
-        <is>
-          <t>EUR 10K MRR</t>
-        </is>
-      </c>
-      <c r="B64" s="183" t="inlineStr">
-        <is>
-          <t>+2%</t>
-        </is>
-      </c>
-      <c r="C64" s="138" t="inlineStr">
-        <is>
-          <t>+1%</t>
-        </is>
-      </c>
-      <c r="D64" s="136" t="inlineStr">
-        <is>
-          <t>Cash-flow breakeven territory</t>
-        </is>
-      </c>
-      <c r="E64" s="127" t="n"/>
-      <c r="F64" s="127" t="n"/>
-      <c r="G64" s="127" t="n"/>
-      <c r="H64" s="127" t="n"/>
-      <c r="I64" s="127" t="n"/>
-    </row>
-    <row r="65" ht="19.5" customHeight="1" s="125">
-      <c r="A65" s="134" t="inlineStr">
-        <is>
-          <t>25 hotels (Stage B)</t>
-        </is>
-      </c>
-      <c r="B65" s="183" t="inlineStr">
-        <is>
-          <t>+3%</t>
-        </is>
-      </c>
-      <c r="C65" s="134" t="inlineStr">
-        <is>
-          <t>+1%</t>
-        </is>
-      </c>
-      <c r="D65" s="136" t="inlineStr">
-        <is>
-          <t>Scale proof — ready for first hires</t>
-        </is>
-      </c>
-      <c r="E65" s="127" t="n"/>
-      <c r="F65" s="127" t="n"/>
-      <c r="G65" s="127" t="n"/>
-      <c r="H65" s="127" t="n"/>
-      <c r="I65" s="127" t="n"/>
-    </row>
-    <row r="66" ht="19.5" customHeight="1" s="125">
-      <c r="A66" s="138" t="inlineStr">
-        <is>
-          <t>EUR 100K MRR</t>
-        </is>
-      </c>
-      <c r="B66" s="183" t="inlineStr">
-        <is>
-          <t>+3%</t>
-        </is>
-      </c>
-      <c r="C66" s="138" t="inlineStr">
-        <is>
-          <t>+2%</t>
-        </is>
-      </c>
-      <c r="D66" s="136" t="inlineStr">
-        <is>
-          <t>Series A territory</t>
-        </is>
-      </c>
-      <c r="E66" s="127" t="n"/>
-      <c r="F66" s="127" t="n"/>
-      <c r="G66" s="127" t="n"/>
-      <c r="H66" s="127" t="n"/>
-      <c r="I66" s="127" t="n"/>
-    </row>
-    <row r="67" ht="19.5" customHeight="1" s="125">
-      <c r="A67" s="134" t="inlineStr">
-        <is>
-          <t>Series A closed</t>
-        </is>
-      </c>
-      <c r="B67" s="183" t="inlineStr">
-        <is>
-          <t>+2%</t>
-        </is>
-      </c>
-      <c r="C67" s="134" t="inlineStr">
-        <is>
-          <t>+1%</t>
-        </is>
-      </c>
-      <c r="D67" s="136" t="inlineStr">
-        <is>
-          <t>External validation of value</t>
-        </is>
-      </c>
-      <c r="E67" s="127" t="n"/>
-      <c r="F67" s="127" t="n"/>
-      <c r="G67" s="127" t="n"/>
-      <c r="H67" s="127" t="n"/>
-      <c r="I67" s="127" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="125">
-      <c r="A68" s="127" t="n"/>
-      <c r="B68" s="127" t="n"/>
-      <c r="C68" s="127" t="n"/>
-      <c r="D68" s="127" t="n"/>
-      <c r="E68" s="127" t="n"/>
-      <c r="F68" s="127" t="n"/>
-      <c r="G68" s="127" t="n"/>
-      <c r="H68" s="127" t="n"/>
-      <c r="I68" s="127" t="n"/>
-    </row>
-    <row r="69" ht="19.5" customHeight="1" s="125">
-      <c r="A69" s="136" t="inlineStr">
-        <is>
-          <t>Note: Milestone shares come from ESOP pool, not dilution of existing holders.</t>
-        </is>
-      </c>
-      <c r="B69" s="127" t="n"/>
-      <c r="C69" s="127" t="n"/>
-      <c r="D69" s="127" t="n"/>
-      <c r="E69" s="127" t="n"/>
-      <c r="F69" s="127" t="n"/>
-      <c r="G69" s="127" t="n"/>
-      <c r="H69" s="127" t="n"/>
-      <c r="I69" s="127" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="125">
-      <c r="A70" s="127" t="n"/>
-      <c r="B70" s="127" t="n"/>
-      <c r="C70" s="127" t="n"/>
-      <c r="D70" s="127" t="n"/>
-      <c r="E70" s="127" t="n"/>
-      <c r="F70" s="127" t="n"/>
-      <c r="G70" s="127" t="n"/>
-      <c r="H70" s="127" t="n"/>
-      <c r="I70" s="127" t="n"/>
-    </row>
-    <row r="71" ht="24" customHeight="1" s="125">
-      <c r="A71" s="129" t="inlineStr">
-        <is>
-          <t>G. ESOP POOL ALLOCATION PLAN (10% = 100 shares)</t>
-        </is>
-      </c>
-      <c r="B71" s="130" t="n"/>
-      <c r="C71" s="130" t="n"/>
-      <c r="D71" s="130" t="n"/>
-      <c r="E71" s="130" t="n"/>
-      <c r="F71" s="130" t="n"/>
-      <c r="G71" s="130" t="n"/>
-      <c r="H71" s="130" t="n"/>
-      <c r="I71" s="130" t="n"/>
-    </row>
-    <row r="72" ht="21.75" customHeight="1" s="125">
-      <c r="A72" s="131" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B72" s="132" t="inlineStr">
-        <is>
-          <t>Grant Range</t>
-        </is>
-      </c>
-      <c r="C72" s="132" t="inlineStr">
-        <is>
-          <t>Vesting</t>
-        </is>
-      </c>
-      <c r="D72" s="132" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="E72" s="132" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="F72" s="133" t="n"/>
-      <c r="G72" s="133" t="n"/>
-      <c r="H72" s="133" t="n"/>
-      <c r="I72" s="133" t="n"/>
-    </row>
-    <row r="73" ht="19.5" customHeight="1" s="125">
-      <c r="A73" s="134" t="inlineStr">
-        <is>
-          <t>CTO (first technical hire)</t>
-        </is>
-      </c>
-      <c r="B73" s="134" t="inlineStr">
-        <is>
-          <t>2-4%</t>
-        </is>
-      </c>
-      <c r="C73" s="134" t="inlineStr">
-        <is>
-          <t>4yr / 1yr cliff</t>
-        </is>
-      </c>
-      <c r="D73" s="134" t="inlineStr">
-        <is>
-          <t>Month 12-15</t>
-        </is>
-      </c>
-      <c r="E73" s="204" t="inlineStr">
-        <is>
-          <t>https://www.indexventures.com/rewarding-talent/</t>
-        </is>
-      </c>
-      <c r="F73" s="127" t="n"/>
-      <c r="G73" s="127" t="n"/>
-      <c r="H73" s="127" t="n"/>
-      <c r="I73" s="127" t="n"/>
-    </row>
-    <row r="74" ht="19.5" customHeight="1" s="125">
-      <c r="A74" s="138" t="inlineStr">
-        <is>
-          <t>CS Lead</t>
-        </is>
-      </c>
-      <c r="B74" s="138" t="inlineStr">
-        <is>
-          <t>1-2%</t>
-        </is>
-      </c>
-      <c r="C74" s="138" t="inlineStr">
-        <is>
-          <t>4yr / 1yr cliff</t>
-        </is>
-      </c>
-      <c r="D74" s="138" t="inlineStr">
-        <is>
-          <t>Month 12-15</t>
-        </is>
-      </c>
-      <c r="E74" s="204" t="inlineStr">
-        <is>
-          <t>https://www.indexventures.com/rewarding-talent/</t>
-        </is>
-      </c>
-      <c r="F74" s="127" t="n"/>
-      <c r="G74" s="127" t="n"/>
-      <c r="H74" s="127" t="n"/>
-      <c r="I74" s="127" t="n"/>
-    </row>
-    <row r="75" ht="19.5" customHeight="1" s="125">
-      <c r="A75" s="134" t="inlineStr">
-        <is>
-          <t>Engineer #1</t>
-        </is>
-      </c>
-      <c r="B75" s="134" t="inlineStr">
-        <is>
-          <t>1-1.5%</t>
-        </is>
-      </c>
-      <c r="C75" s="134" t="inlineStr">
-        <is>
-          <t>4yr / 1yr cliff</t>
-        </is>
-      </c>
-      <c r="D75" s="134" t="inlineStr">
-        <is>
-          <t>Month 18-24</t>
-        </is>
-      </c>
-      <c r="E75" s="127" t="n"/>
-      <c r="F75" s="127" t="n"/>
-      <c r="G75" s="127" t="n"/>
-      <c r="H75" s="127" t="n"/>
-      <c r="I75" s="127" t="n"/>
-    </row>
-    <row r="76" ht="19.5" customHeight="1" s="125">
-      <c r="A76" s="138" t="inlineStr">
-        <is>
-          <t>Engineer #2</t>
-        </is>
-      </c>
-      <c r="B76" s="138" t="inlineStr">
-        <is>
-          <t>0.5-1%</t>
-        </is>
-      </c>
-      <c r="C76" s="138" t="inlineStr">
-        <is>
-          <t>4yr / 1yr cliff</t>
-        </is>
-      </c>
-      <c r="D76" s="138" t="inlineStr">
-        <is>
-          <t>Month 24-30</t>
-        </is>
-      </c>
-      <c r="E76" s="127" t="n"/>
-      <c r="F76" s="127" t="n"/>
-      <c r="G76" s="127" t="n"/>
-      <c r="H76" s="127" t="n"/>
-      <c r="I76" s="127" t="n"/>
-    </row>
-    <row r="77" ht="19.5" customHeight="1" s="125">
-      <c r="A77" s="134" t="inlineStr">
-        <is>
-          <t>Sales/BD hire</t>
-        </is>
-      </c>
-      <c r="B77" s="134" t="inlineStr">
-        <is>
-          <t>0.5-1%</t>
-        </is>
-      </c>
-      <c r="C77" s="134" t="inlineStr">
-        <is>
-          <t>4yr / 1yr cliff</t>
-        </is>
-      </c>
-      <c r="D77" s="134" t="inlineStr">
-        <is>
-          <t>Month 24-30</t>
-        </is>
-      </c>
-      <c r="E77" s="127" t="n"/>
-      <c r="F77" s="127" t="n"/>
-      <c r="G77" s="127" t="n"/>
-      <c r="H77" s="127" t="n"/>
-      <c r="I77" s="127" t="n"/>
-    </row>
-    <row r="78" ht="19.5" customHeight="1" s="125">
-      <c r="A78" s="138" t="inlineStr">
-        <is>
-          <t>RESERVED for future</t>
-        </is>
-      </c>
-      <c r="B78" s="138" t="inlineStr">
-        <is>
-          <t>1-3%</t>
-        </is>
-      </c>
-      <c r="C78" s="138" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D78" s="138" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="127" t="n"/>
-      <c r="F78" s="127" t="n"/>
-      <c r="G78" s="127" t="n"/>
-      <c r="H78" s="127" t="n"/>
-      <c r="I78" s="127" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" s="125">
-      <c r="A79" s="127" t="n"/>
-      <c r="B79" s="127" t="n"/>
-      <c r="C79" s="127" t="n"/>
-      <c r="D79" s="127" t="n"/>
-      <c r="E79" s="127" t="n"/>
-      <c r="F79" s="127" t="n"/>
-      <c r="G79" s="127" t="n"/>
-      <c r="H79" s="127" t="n"/>
-      <c r="I79" s="127" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1" s="125">
-      <c r="A80" s="127" t="n"/>
-      <c r="B80" s="127" t="n"/>
-      <c r="C80" s="127" t="n"/>
-      <c r="D80" s="127" t="n"/>
-      <c r="E80" s="127" t="n"/>
-      <c r="F80" s="127" t="n"/>
-      <c r="G80" s="127" t="n"/>
-      <c r="H80" s="127" t="n"/>
-      <c r="I80" s="127" t="n"/>
-    </row>
-    <row r="81" ht="24" customHeight="1" s="125">
-      <c r="A81" s="129" t="inlineStr">
-        <is>
-          <t>H. SOURCES</t>
-        </is>
-      </c>
-      <c r="B81" s="130" t="n"/>
-      <c r="C81" s="130" t="n"/>
-      <c r="D81" s="130" t="n"/>
-      <c r="E81" s="130" t="n"/>
-      <c r="F81" s="130" t="n"/>
-      <c r="G81" s="130" t="n"/>
-      <c r="H81" s="130" t="n"/>
-      <c r="I81" s="130" t="n"/>
-    </row>
-    <row r="82" ht="19.5" customHeight="1" s="125">
-      <c r="A82" s="134" t="inlineStr">
-        <is>
-          <t>Y Combinator: Equity Split Guide</t>
-        </is>
-      </c>
-      <c r="B82" s="204" t="inlineStr">
-        <is>
-          <t>https://www.ycombinator.com/library/5x-how-to-split-equity-among-co-founders</t>
-        </is>
-      </c>
-      <c r="C82" s="127" t="n"/>
-      <c r="D82" s="127" t="n"/>
-      <c r="E82" s="127" t="n"/>
-      <c r="F82" s="127" t="n"/>
-      <c r="G82" s="127" t="n"/>
-      <c r="H82" s="127" t="n"/>
-      <c r="I82" s="127" t="n"/>
-    </row>
-    <row r="83" ht="19.5" customHeight="1" s="125">
-      <c r="A83" s="138" t="inlineStr">
-        <is>
-          <t>Slicing Pie: Dynamic Equity Framework</t>
-        </is>
-      </c>
-      <c r="B83" s="204" t="inlineStr">
-        <is>
-          <t>https://slicingpie.com</t>
-        </is>
-      </c>
-      <c r="C83" s="127" t="n"/>
-      <c r="D83" s="127" t="n"/>
-      <c r="E83" s="127" t="n"/>
-      <c r="F83" s="127" t="n"/>
-      <c r="G83" s="127" t="n"/>
-      <c r="H83" s="127" t="n"/>
-      <c r="I83" s="127" t="n"/>
-    </row>
-    <row r="84" ht="19.5" customHeight="1" s="125">
-      <c r="A84" s="134" t="inlineStr">
-        <is>
-          <t>Carta: Founder Equity Split Trends 2024</t>
-        </is>
-      </c>
-      <c r="B84" s="204" t="inlineStr">
-        <is>
-          <t>https://carta.com/data/founder-equity-split-trends-2024/</t>
-        </is>
-      </c>
-      <c r="C84" s="127" t="n"/>
-      <c r="D84" s="127" t="n"/>
-      <c r="E84" s="127" t="n"/>
-      <c r="F84" s="127" t="n"/>
-      <c r="G84" s="127" t="n"/>
-      <c r="H84" s="127" t="n"/>
-      <c r="I84" s="127" t="n"/>
-    </row>
-    <row r="85" ht="19.5" customHeight="1" s="125">
-      <c r="A85" s="138" t="inlineStr">
-        <is>
-          <t>Creandum: Founder Compensation Survey 2025</t>
-        </is>
-      </c>
-      <c r="B85" s="204" t="inlineStr">
-        <is>
-          <t>https://www.creandum.com/reports/founder-compensation-2025</t>
-        </is>
-      </c>
-      <c r="C85" s="127" t="n"/>
-      <c r="D85" s="127" t="n"/>
-      <c r="E85" s="127" t="n"/>
-      <c r="F85" s="127" t="n"/>
-      <c r="G85" s="127" t="n"/>
-      <c r="H85" s="127" t="n"/>
-      <c r="I85" s="127" t="n"/>
-    </row>
-    <row r="86" ht="19.5" customHeight="1" s="125">
-      <c r="A86" s="134" t="inlineStr">
-        <is>
-          <t>Index Ventures: ESOP Sizing at Seed</t>
-        </is>
-      </c>
-      <c r="B86" s="204" t="inlineStr">
-        <is>
-          <t>https://www.indexventures.com/rewarding-talent/esop-size-at-seed</t>
-        </is>
-      </c>
-      <c r="C86" s="127" t="n"/>
-      <c r="D86" s="127" t="n"/>
-      <c r="E86" s="127" t="n"/>
-      <c r="F86" s="127" t="n"/>
-      <c r="G86" s="127" t="n"/>
-      <c r="H86" s="127" t="n"/>
-      <c r="I86" s="127" t="n"/>
-    </row>
-    <row r="87" ht="19.5" customHeight="1" s="125">
-      <c r="A87" s="138" t="inlineStr">
-        <is>
-          <t>Corporate Finance Institute: Sweat Equity</t>
-        </is>
-      </c>
-      <c r="B87" s="204" t="inlineStr">
-        <is>
-          <t>https://corporatefinanceinstitute.com/resources/valuation/sweat-equity/</t>
-        </is>
-      </c>
-      <c r="C87" s="127" t="n"/>
-      <c r="D87" s="127" t="n"/>
-      <c r="E87" s="127" t="n"/>
-      <c r="F87" s="127" t="n"/>
-      <c r="G87" s="127" t="n"/>
-      <c r="H87" s="127" t="n"/>
-      <c r="I87" s="127" t="n"/>
-    </row>
-    <row r="88" ht="19.5" customHeight="1" s="125">
-      <c r="A88" s="134" t="inlineStr">
-        <is>
-          <t>Ravio: AI-Native Compensation 2025</t>
-        </is>
-      </c>
-      <c r="B88" s="204" t="inlineStr">
-        <is>
-          <t>https://ravio.com/reports/ai-native-compensation-2025/</t>
-        </is>
-      </c>
-      <c r="C88" s="127" t="n"/>
-      <c r="D88" s="127" t="n"/>
-      <c r="E88" s="127" t="n"/>
-      <c r="F88" s="127" t="n"/>
-      <c r="G88" s="127" t="n"/>
-      <c r="H88" s="127" t="n"/>
-      <c r="I88" s="127" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B44:E44"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16622,7 +13255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17400,7 +14033,7 @@
       <c r="C45" s="157" t="n"/>
       <c r="D45" s="157" t="inlineStr">
         <is>
-          <t>Seed CHF 120-150K only. No VC dilution beyond founding.</t>
+          <t>Seed CHF 120-150K only. No later financing assumed.</t>
         </is>
       </c>
       <c r="E45" s="157" t="n"/>
@@ -17472,7 +14105,7 @@
     <row r="53" ht="15" customHeight="1" s="125">
       <c r="A53" s="211" t="inlineStr">
         <is>
-          <t>M60 P50: 227 hotels, EUR 9.21M ARR, EUR 46M exit at 5x. No VC dilution.</t>
+          <t>M60 P50: 227 hotels, EUR 9.21M ARR, EUR 46M exit at 5x. No later financing assumed.</t>
         </is>
       </c>
     </row>
@@ -17497,7 +14130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18800,4 +15433,1483 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:G79"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="36" customWidth="1" style="124" min="1" max="1"/>
+    <col width="16" customWidth="1" style="124" min="2" max="6"/>
+    <col width="30" customWidth="1" style="124" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1" s="125">
+      <c r="A1" s="210" t="inlineStr">
+        <is>
+          <t>TERCIER — Scenario C: Historical VC-Accelerated (exploratory, P50 retained)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="125">
+      <c r="A2" s="211" t="inlineStr">
+        <is>
+          <t>Historical exploratory sheet retained for comparison only. Hotel milestones were reduced to the internally consistent P50 path used by the retained ARR / P&amp;L snapshot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="125">
+      <c r="A4" s="163" t="inlineStr">
+        <is>
+          <t>CAPITAL STRUCTURE</t>
+        </is>
+      </c>
+      <c r="B4" s="164" t="n"/>
+      <c r="C4" s="164" t="n"/>
+      <c r="D4" s="164" t="n"/>
+      <c r="E4" s="164" t="n"/>
+      <c r="F4" s="164" t="n"/>
+      <c r="G4" s="164" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="125">
+      <c r="A5" s="212" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B5" s="218" t="inlineStr">
+        <is>
+          <t>Amount (EUR)</t>
+        </is>
+      </c>
+      <c r="C5" s="218" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="D5" s="218" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E5" s="218" t="n"/>
+      <c r="F5" s="218" t="n"/>
+      <c r="G5" s="218" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="125">
+      <c r="A6" s="214" t="inlineStr">
+        <is>
+          <t>Seed (CHF 150K → EUR)</t>
+        </is>
+      </c>
+      <c r="B6" s="216" t="n">
+        <v>164835</v>
+      </c>
+      <c r="C6" s="214" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="D6" s="214" t="inlineStr">
+        <is>
+          <t>Guffanti/Corsaro operator seed</t>
+        </is>
+      </c>
+      <c r="E6" s="214" t="n"/>
+      <c r="F6" s="214" t="n"/>
+      <c r="G6" s="214" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="125">
+      <c r="A7" s="157" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B7" s="215" t="n">
+        <v>55556</v>
+      </c>
+      <c r="C7" s="157" t="inlineStr">
+        <is>
+          <t>M0</t>
+        </is>
+      </c>
+      <c r="D7" s="157" t="inlineStr">
+        <is>
+          <t>AG incorporation</t>
+        </is>
+      </c>
+      <c r="E7" s="157" t="n"/>
+      <c r="F7" s="157" t="n"/>
+      <c r="G7" s="157" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="125">
+      <c r="A8" s="214" t="inlineStr">
+        <is>
+          <t>Series A (strategic)</t>
+        </is>
+      </c>
+      <c r="B8" s="216" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="C8" s="214" t="inlineStr">
+        <is>
+          <t>M27</t>
+        </is>
+      </c>
+      <c r="D8" s="214" t="inlineStr">
+        <is>
+          <t>Hospitality-specific investor. Raise from strength.</t>
+        </is>
+      </c>
+      <c r="E8" s="214" t="n"/>
+      <c r="F8" s="214" t="n"/>
+      <c r="G8" s="214" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="125">
+      <c r="A9" s="160" t="inlineStr">
+        <is>
+          <t>Total capital</t>
+        </is>
+      </c>
+      <c r="B9" s="222" t="n">
+        <v>4277778</v>
+      </c>
+      <c r="C9" s="160" t="n"/>
+      <c r="D9" s="160" t="inlineStr">
+        <is>
+          <t>vs EUR 277K in operator-seeded paths</t>
+        </is>
+      </c>
+      <c r="E9" s="160" t="n"/>
+      <c r="F9" s="160" t="n"/>
+      <c r="G9" s="160" t="n"/>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="125">
+      <c r="A11" s="163" t="inlineStr">
+        <is>
+          <t>HOTEL MILESTONES (P50 path retained from monthly snapshot)</t>
+        </is>
+      </c>
+      <c r="B11" s="164" t="n"/>
+      <c r="C11" s="164" t="n"/>
+      <c r="D11" s="164" t="n"/>
+      <c r="E11" s="164" t="n"/>
+      <c r="F11" s="164" t="n"/>
+      <c r="G11" s="164" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="125">
+      <c r="A12" s="212" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="B12" s="165" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="C12" s="165" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D12" s="165" t="n"/>
+      <c r="E12" s="165" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="F12" s="165" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="G12" s="165" t="inlineStr">
+        <is>
+          <t>vs Scenario A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="125">
+      <c r="A13" s="214" t="inlineStr">
+        <is>
+          <t>Month 6</t>
+        </is>
+      </c>
+      <c r="B13" s="223" t="n">
+        <v>14</v>
+      </c>
+      <c r="C13" s="223" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D13" s="216" t="n"/>
+      <c r="E13" s="223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="223" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="125">
+      <c r="A14" s="157" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="B14" s="215" t="n">
+        <v>21</v>
+      </c>
+      <c r="C14" s="224" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D14" s="215" t="n"/>
+      <c r="E14" s="224" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="215" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" s="157" t="inlineStr">
+        <is>
+          <t>+6</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="125">
+      <c r="A15" s="214" t="inlineStr">
+        <is>
+          <t>Month 18</t>
+        </is>
+      </c>
+      <c r="B15" s="216" t="n">
+        <v>62</v>
+      </c>
+      <c r="C15" s="225" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D15" s="216" t="n"/>
+      <c r="E15" s="225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="216" t="n">
+        <v>48</v>
+      </c>
+      <c r="G15" s="214" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="125">
+      <c r="A16" s="157" t="inlineStr">
+        <is>
+          <t>Month 24</t>
+        </is>
+      </c>
+      <c r="B16" s="215" t="n">
+        <v>99</v>
+      </c>
+      <c r="C16" s="215" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D16" s="215" t="n"/>
+      <c r="E16" s="215" t="n">
+        <v>115</v>
+      </c>
+      <c r="F16" s="215" t="n">
+        <v>129</v>
+      </c>
+      <c r="G16" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="125">
+      <c r="A17" s="214" t="inlineStr">
+        <is>
+          <t>Month 36</t>
+        </is>
+      </c>
+      <c r="B17" s="216" t="n">
+        <v>502</v>
+      </c>
+      <c r="C17" s="225" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D17" s="216" t="n"/>
+      <c r="E17" s="225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="216" t="n">
+        <v>135</v>
+      </c>
+      <c r="G17" s="214" t="inlineStr">
+        <is>
+          <t>+28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="125">
+      <c r="A18" s="157" t="inlineStr">
+        <is>
+          <t>Month 48</t>
+        </is>
+      </c>
+      <c r="B18" s="215" t="n">
+        <v>818</v>
+      </c>
+      <c r="C18" s="215" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D18" s="215" t="n"/>
+      <c r="E18" s="215" t="n">
+        <v>931</v>
+      </c>
+      <c r="F18" s="215" t="n">
+        <v>1038</v>
+      </c>
+      <c r="G18" s="157" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="125">
+      <c r="A19" s="214" t="inlineStr">
+        <is>
+          <t>Month 60</t>
+        </is>
+      </c>
+      <c r="B19" s="216" t="n">
+        <v>886</v>
+      </c>
+      <c r="C19" s="225" t="inlineStr">
+        <is>
+          <t>Retained P50 path</t>
+        </is>
+      </c>
+      <c r="D19" s="216" t="n"/>
+      <c r="E19" s="225" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="216" t="n">
+        <v>424</v>
+      </c>
+      <c r="G19" s="214" t="inlineStr">
+        <is>
+          <t>+128</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="125">
+      <c r="A21" s="163" t="inlineStr">
+        <is>
+          <t>ARR TRAJECTORY (EUR)</t>
+        </is>
+      </c>
+      <c r="B21" s="164" t="n"/>
+      <c r="C21" s="164" t="n"/>
+      <c r="D21" s="164" t="n"/>
+      <c r="E21" s="164" t="n"/>
+      <c r="F21" s="164" t="n"/>
+      <c r="G21" s="164" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="125">
+      <c r="A22" s="212" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="B22" s="165" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C22" s="165" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="D22" s="165" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="E22" s="165" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="F22" s="165" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="G22" s="165" t="inlineStr">
+        <is>
+          <t>vs Scenario A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="125">
+      <c r="A23" s="214" t="inlineStr">
+        <is>
+          <t>Month 12</t>
+        </is>
+      </c>
+      <c r="B23" s="216" t="n">
+        <v>323423</v>
+      </c>
+      <c r="C23" s="216" t="n">
+        <v>391209</v>
+      </c>
+      <c r="D23" s="216" t="n">
+        <v>486928</v>
+      </c>
+      <c r="E23" s="216" t="n">
+        <v>606000</v>
+      </c>
+      <c r="F23" s="216" t="n">
+        <v>733277</v>
+      </c>
+      <c r="G23" s="214" t="inlineStr">
+        <is>
+          <t>+5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="125">
+      <c r="A24" s="157" t="inlineStr">
+        <is>
+          <t>Month 18</t>
+        </is>
+      </c>
+      <c r="B24" s="215" t="n">
+        <v>989324</v>
+      </c>
+      <c r="C24" s="215" t="n">
+        <v>1246506</v>
+      </c>
+      <c r="D24" s="215" t="n">
+        <v>1547509</v>
+      </c>
+      <c r="E24" s="215" t="n">
+        <v>1878612</v>
+      </c>
+      <c r="F24" s="215" t="n">
+        <v>2202507</v>
+      </c>
+      <c r="G24" s="157" t="inlineStr">
+        <is>
+          <t>+99%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="125">
+      <c r="A25" s="214" t="inlineStr">
+        <is>
+          <t>Month 24</t>
+        </is>
+      </c>
+      <c r="B25" s="216" t="n">
+        <v>1703047</v>
+      </c>
+      <c r="C25" s="216" t="n">
+        <v>2076296</v>
+      </c>
+      <c r="D25" s="216" t="n">
+        <v>2582714</v>
+      </c>
+      <c r="E25" s="216" t="n">
+        <v>3173308</v>
+      </c>
+      <c r="F25" s="216" t="n">
+        <v>3767253</v>
+      </c>
+      <c r="G25" s="214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="125">
+      <c r="A26" s="157" t="inlineStr">
+        <is>
+          <t>Month 36</t>
+        </is>
+      </c>
+      <c r="B26" s="215" t="n">
+        <v>10387079</v>
+      </c>
+      <c r="C26" s="215" t="n">
+        <v>13212060</v>
+      </c>
+      <c r="D26" s="215" t="n">
+        <v>16735554</v>
+      </c>
+      <c r="E26" s="215" t="n">
+        <v>20665691</v>
+      </c>
+      <c r="F26" s="215" t="n">
+        <v>24553645</v>
+      </c>
+      <c r="G26" s="157" t="inlineStr">
+        <is>
+          <t>+549%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="125">
+      <c r="A27" s="214" t="inlineStr">
+        <is>
+          <t>Month 48</t>
+        </is>
+      </c>
+      <c r="B27" s="216" t="n">
+        <v>22783966</v>
+      </c>
+      <c r="C27" s="216" t="n">
+        <v>25639903</v>
+      </c>
+      <c r="D27" s="216" t="n">
+        <v>29604998</v>
+      </c>
+      <c r="E27" s="216" t="n">
+        <v>34852501</v>
+      </c>
+      <c r="F27" s="216" t="n">
+        <v>40716173</v>
+      </c>
+      <c r="G27" s="214" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="125">
+      <c r="A28" s="157" t="inlineStr">
+        <is>
+          <t>Month 60</t>
+        </is>
+      </c>
+      <c r="B28" s="215" t="n">
+        <v>24926447</v>
+      </c>
+      <c r="C28" s="215" t="n">
+        <v>28069088</v>
+      </c>
+      <c r="D28" s="215" t="n">
+        <v>34055136</v>
+      </c>
+      <c r="E28" s="215" t="n">
+        <v>44751357</v>
+      </c>
+      <c r="F28" s="215" t="n">
+        <v>55550176</v>
+      </c>
+      <c r="G28" s="157" t="inlineStr">
+        <is>
+          <t>+288%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="125">
+      <c r="A30" s="163" t="inlineStr">
+        <is>
+          <t>MONTHLY P&amp;L SNAPSHOT (P50, EUR)</t>
+        </is>
+      </c>
+      <c r="B30" s="164" t="n"/>
+      <c r="C30" s="164" t="n"/>
+      <c r="D30" s="164" t="n"/>
+      <c r="E30" s="164" t="n"/>
+      <c r="F30" s="164" t="n"/>
+      <c r="G30" s="164" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="125">
+      <c r="A31" s="212" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B31" s="218" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="C31" s="218" t="inlineStr">
+        <is>
+          <t>Hotels</t>
+        </is>
+      </c>
+      <c r="D31" s="218" t="inlineStr">
+        <is>
+          <t>Total Costs</t>
+        </is>
+      </c>
+      <c r="E31" s="218" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="F31" s="218" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="G31" s="218" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="125">
+      <c r="A32" s="214" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B32" s="216" t="n">
+        <v>3635</v>
+      </c>
+      <c r="C32" s="216" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="216" t="n">
+        <v>11173</v>
+      </c>
+      <c r="E32" s="216" t="n">
+        <v>-7972</v>
+      </c>
+      <c r="F32" s="216" t="n">
+        <v>269806</v>
+      </c>
+      <c r="G32" s="216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="125">
+      <c r="A33" s="157" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B33" s="215" t="n">
+        <v>26339</v>
+      </c>
+      <c r="C33" s="215" t="n">
+        <v>14</v>
+      </c>
+      <c r="D33" s="215" t="n">
+        <v>14945</v>
+      </c>
+      <c r="E33" s="215" t="n">
+        <v>7381</v>
+      </c>
+      <c r="F33" s="215" t="n">
+        <v>269850</v>
+      </c>
+      <c r="G33" s="215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="125">
+      <c r="A34" s="214" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B34" s="216" t="n">
+        <v>40577</v>
+      </c>
+      <c r="C34" s="216" t="n">
+        <v>21</v>
+      </c>
+      <c r="D34" s="216" t="n">
+        <v>35321</v>
+      </c>
+      <c r="E34" s="216" t="n">
+        <v>5207</v>
+      </c>
+      <c r="F34" s="216" t="n">
+        <v>299813</v>
+      </c>
+      <c r="G34" s="216" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="125">
+      <c r="A35" s="157" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="B35" s="215" t="n">
+        <v>128959</v>
+      </c>
+      <c r="C35" s="215" t="n">
+        <v>62</v>
+      </c>
+      <c r="D35" s="215" t="n">
+        <v>59454</v>
+      </c>
+      <c r="E35" s="215" t="n">
+        <v>70422</v>
+      </c>
+      <c r="F35" s="215" t="n">
+        <v>485101</v>
+      </c>
+      <c r="G35" s="215" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="125">
+      <c r="A36" s="214" t="inlineStr">
+        <is>
+          <t>M24</t>
+        </is>
+      </c>
+      <c r="B36" s="216" t="n">
+        <v>215226</v>
+      </c>
+      <c r="C36" s="216" t="n">
+        <v>99</v>
+      </c>
+      <c r="D36" s="216" t="n">
+        <v>63570</v>
+      </c>
+      <c r="E36" s="216" t="n">
+        <v>151393</v>
+      </c>
+      <c r="F36" s="216" t="n">
+        <v>1132290</v>
+      </c>
+      <c r="G36" s="216" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="125">
+      <c r="A37" s="226" t="inlineStr">
+        <is>
+          <t>M27</t>
+        </is>
+      </c>
+      <c r="B37" s="227" t="n">
+        <v>281531</v>
+      </c>
+      <c r="C37" s="227" t="n">
+        <v>128</v>
+      </c>
+      <c r="D37" s="227" t="n">
+        <v>67755</v>
+      </c>
+      <c r="E37" s="227" t="n">
+        <v>213921</v>
+      </c>
+      <c r="F37" s="227" t="n">
+        <v>5708048</v>
+      </c>
+      <c r="G37" s="228" t="inlineStr">
+        <is>
+          <t>← Series A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="125">
+      <c r="A38" s="214" t="inlineStr">
+        <is>
+          <t>M30</t>
+        </is>
+      </c>
+      <c r="B38" s="216" t="n">
+        <v>390113</v>
+      </c>
+      <c r="C38" s="216" t="n">
+        <v>172</v>
+      </c>
+      <c r="D38" s="216" t="n">
+        <v>112654</v>
+      </c>
+      <c r="E38" s="216" t="n">
+        <v>276644</v>
+      </c>
+      <c r="F38" s="216" t="n">
+        <v>6496623</v>
+      </c>
+      <c r="G38" s="216" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="125">
+      <c r="A39" s="157" t="inlineStr">
+        <is>
+          <t>M33</t>
+        </is>
+      </c>
+      <c r="B39" s="215" t="n">
+        <v>649097</v>
+      </c>
+      <c r="C39" s="215" t="n">
+        <v>240</v>
+      </c>
+      <c r="D39" s="215" t="n">
+        <v>127799</v>
+      </c>
+      <c r="E39" s="215" t="n">
+        <v>521135</v>
+      </c>
+      <c r="F39" s="215" t="n">
+        <v>7636526</v>
+      </c>
+      <c r="G39" s="215" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="125">
+      <c r="A40" s="214" t="inlineStr">
+        <is>
+          <t>M36</t>
+        </is>
+      </c>
+      <c r="B40" s="216" t="n">
+        <v>1394629</v>
+      </c>
+      <c r="C40" s="216" t="n">
+        <v>502</v>
+      </c>
+      <c r="D40" s="216" t="n">
+        <v>172481</v>
+      </c>
+      <c r="E40" s="216" t="n">
+        <v>1221982</v>
+      </c>
+      <c r="F40" s="216" t="n">
+        <v>10522913</v>
+      </c>
+      <c r="G40" s="216" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="125">
+      <c r="A41" s="157" t="inlineStr">
+        <is>
+          <t>M42</t>
+        </is>
+      </c>
+      <c r="B41" s="215" t="n">
+        <v>2248036</v>
+      </c>
+      <c r="C41" s="215" t="n">
+        <v>780</v>
+      </c>
+      <c r="D41" s="215" t="n">
+        <v>222336</v>
+      </c>
+      <c r="E41" s="215" t="n">
+        <v>2024848</v>
+      </c>
+      <c r="F41" s="215" t="n">
+        <v>21123515</v>
+      </c>
+      <c r="G41" s="215" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="125">
+      <c r="A42" s="214" t="inlineStr">
+        <is>
+          <t>M48</t>
+        </is>
+      </c>
+      <c r="B42" s="216" t="n">
+        <v>2467083</v>
+      </c>
+      <c r="C42" s="216" t="n">
+        <v>818</v>
+      </c>
+      <c r="D42" s="216" t="n">
+        <v>235833</v>
+      </c>
+      <c r="E42" s="216" t="n">
+        <v>2232438</v>
+      </c>
+      <c r="F42" s="216" t="n">
+        <v>33707725</v>
+      </c>
+      <c r="G42" s="216" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="125">
+      <c r="A43" s="157" t="inlineStr">
+        <is>
+          <t>M54</t>
+        </is>
+      </c>
+      <c r="B43" s="215" t="n">
+        <v>2669239</v>
+      </c>
+      <c r="C43" s="215" t="n">
+        <v>858</v>
+      </c>
+      <c r="D43" s="215" t="n">
+        <v>247128</v>
+      </c>
+      <c r="E43" s="215" t="n">
+        <v>2421366</v>
+      </c>
+      <c r="F43" s="215" t="n">
+        <v>47666864</v>
+      </c>
+      <c r="G43" s="215" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="125">
+      <c r="A44" s="214" t="inlineStr">
+        <is>
+          <t>M60</t>
+        </is>
+      </c>
+      <c r="B44" s="216" t="n">
+        <v>2837928</v>
+      </c>
+      <c r="C44" s="216" t="n">
+        <v>886</v>
+      </c>
+      <c r="D44" s="216" t="n">
+        <v>257064</v>
+      </c>
+      <c r="E44" s="216" t="n">
+        <v>2581774</v>
+      </c>
+      <c r="F44" s="216" t="n">
+        <v>62491641</v>
+      </c>
+      <c r="G44" s="216" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="125">
+      <c r="A46" s="163" t="inlineStr">
+        <is>
+          <t>MILESTONE PROBABILITIES</t>
+        </is>
+      </c>
+      <c r="B46" s="164" t="n"/>
+      <c r="C46" s="164" t="n"/>
+      <c r="D46" s="164" t="n"/>
+      <c r="E46" s="164" t="n"/>
+      <c r="F46" s="164" t="n"/>
+      <c r="G46" s="164" t="n"/>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="125">
+      <c r="A47" s="212" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="B47" s="218" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="C47" s="218" t="n"/>
+      <c r="D47" s="218" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="E47" s="218" t="n"/>
+      <c r="F47" s="218" t="n"/>
+      <c r="G47" s="218" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="125">
+      <c r="A48" s="214" t="inlineStr">
+        <is>
+          <t>5 hotels by M12</t>
+        </is>
+      </c>
+      <c r="B48" s="219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="214" t="n"/>
+      <c r="D48" s="214" t="n"/>
+      <c r="E48" s="214" t="n"/>
+      <c r="F48" s="214" t="n"/>
+      <c r="G48" s="214" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="125">
+      <c r="A49" s="157" t="inlineStr">
+        <is>
+          <t>€25K MRR by M18</t>
+        </is>
+      </c>
+      <c r="B49" s="220" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="C49" s="157" t="n"/>
+      <c r="D49" s="157" t="n"/>
+      <c r="E49" s="157" t="n"/>
+      <c r="F49" s="157" t="n"/>
+      <c r="G49" s="157" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="125">
+      <c r="A50" s="214" t="inlineStr">
+        <is>
+          <t>€75K MRR by M24</t>
+        </is>
+      </c>
+      <c r="B50" s="219" t="n">
+        <v>0.9992</v>
+      </c>
+      <c r="C50" s="214" t="n"/>
+      <c r="D50" s="214" t="n"/>
+      <c r="E50" s="214" t="n"/>
+      <c r="F50" s="214" t="n"/>
+      <c r="G50" s="214" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="125">
+      <c r="A51" s="157" t="inlineStr">
+        <is>
+          <t>€1M ARR by M24</t>
+        </is>
+      </c>
+      <c r="B51" s="220" t="n">
+        <v>0.9981</v>
+      </c>
+      <c r="C51" s="157" t="n"/>
+      <c r="D51" s="157" t="n"/>
+      <c r="E51" s="157" t="n"/>
+      <c r="F51" s="157" t="n"/>
+      <c r="G51" s="157" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="125">
+      <c r="A52" s="214" t="inlineStr">
+        <is>
+          <t>€5M ARR by M36</t>
+        </is>
+      </c>
+      <c r="B52" s="219" t="n">
+        <v>0.9978</v>
+      </c>
+      <c r="C52" s="214" t="n"/>
+      <c r="D52" s="214" t="n"/>
+      <c r="E52" s="214" t="n"/>
+      <c r="F52" s="214" t="n"/>
+      <c r="G52" s="214" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="125">
+      <c r="A53" s="157" t="inlineStr">
+        <is>
+          <t>€10M ARR by M48</t>
+        </is>
+      </c>
+      <c r="B53" s="220" t="n">
+        <v>0.9989</v>
+      </c>
+      <c r="C53" s="157" t="n"/>
+      <c r="D53" s="157" t="n"/>
+      <c r="E53" s="157" t="n"/>
+      <c r="F53" s="157" t="n"/>
+      <c r="G53" s="157" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="125">
+      <c r="A54" s="214" t="inlineStr">
+        <is>
+          <t>€15M ARR by M60</t>
+        </is>
+      </c>
+      <c r="B54" s="219" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="C54" s="214" t="n"/>
+      <c r="D54" s="214" t="n"/>
+      <c r="E54" s="214" t="n"/>
+      <c r="F54" s="214" t="n"/>
+      <c r="G54" s="214" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="125">
+      <c r="A55" s="157" t="inlineStr">
+        <is>
+          <t>€20M ARR by M60</t>
+        </is>
+      </c>
+      <c r="B55" s="220" t="n">
+        <v>0.9892</v>
+      </c>
+      <c r="C55" s="157" t="n"/>
+      <c r="D55" s="157" t="n"/>
+      <c r="E55" s="157" t="n"/>
+      <c r="F55" s="157" t="n"/>
+      <c r="G55" s="157" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="125">
+      <c r="A56" s="214" t="inlineStr">
+        <is>
+          <t>Breakeven by M9</t>
+        </is>
+      </c>
+      <c r="B56" s="219" t="n">
+        <v>0.9782</v>
+      </c>
+      <c r="C56" s="214" t="n"/>
+      <c r="D56" s="214" t="n"/>
+      <c r="E56" s="214" t="n"/>
+      <c r="F56" s="214" t="n"/>
+      <c r="G56" s="214" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="125">
+      <c r="A57" s="157" t="inlineStr">
+        <is>
+          <t>Breakeven by M12</t>
+        </is>
+      </c>
+      <c r="B57" s="220" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="C57" s="157" t="n"/>
+      <c r="D57" s="157" t="n"/>
+      <c r="E57" s="157" t="n"/>
+      <c r="F57" s="157" t="n"/>
+      <c r="G57" s="157" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="125">
+      <c r="A58" s="214" t="inlineStr">
+        <is>
+          <t>Cash negative ever</t>
+        </is>
+      </c>
+      <c r="B58" s="219" t="n">
+        <v>0.0007</v>
+      </c>
+      <c r="C58" s="214" t="n"/>
+      <c r="D58" s="214" t="n"/>
+      <c r="E58" s="214" t="n"/>
+      <c r="F58" s="214" t="n"/>
+      <c r="G58" s="214" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="125">
+      <c r="A59" s="157" t="inlineStr">
+        <is>
+          <t>€100M exit (4x) by M60</t>
+        </is>
+      </c>
+      <c r="B59" s="220" t="n">
+        <v>0.8966</v>
+      </c>
+      <c r="C59" s="157" t="n"/>
+      <c r="D59" s="157" t="n"/>
+      <c r="E59" s="157" t="n"/>
+      <c r="F59" s="157" t="n"/>
+      <c r="G59" s="157" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="125">
+      <c r="A60" s="214" t="inlineStr">
+        <is>
+          <t>€100M exit (5.5x) by M60</t>
+        </is>
+      </c>
+      <c r="B60" s="219" t="n">
+        <v>0.9933</v>
+      </c>
+      <c r="C60" s="214" t="n"/>
+      <c r="D60" s="214" t="n"/>
+      <c r="E60" s="214" t="n"/>
+      <c r="F60" s="214" t="n"/>
+      <c r="G60" s="214" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="125">
+      <c r="A61" s="157" t="inlineStr">
+        <is>
+          <t>€100M exit (7x) by M60</t>
+        </is>
+      </c>
+      <c r="B61" s="220" t="n">
+        <v>0.9977</v>
+      </c>
+      <c r="C61" s="157" t="n"/>
+      <c r="D61" s="157" t="n"/>
+      <c r="E61" s="157" t="n"/>
+      <c r="F61" s="157" t="n"/>
+      <c r="G61" s="157" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="125">
+      <c r="A62" s="163" t="inlineStr">
+        <is>
+          <t>EXIT VALUATION AT MONTH 60 (EUR)</t>
+        </is>
+      </c>
+      <c r="B62" s="164" t="n"/>
+      <c r="C62" s="164" t="n"/>
+      <c r="D62" s="164" t="n"/>
+      <c r="E62" s="164" t="n"/>
+      <c r="F62" s="164" t="n"/>
+      <c r="G62" s="164" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="125">
+      <c r="A63" s="212" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B63" s="218" t="inlineStr">
+        <is>
+          <t>P10</t>
+        </is>
+      </c>
+      <c r="C63" s="218" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="D63" s="218" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="E63" s="218" t="inlineStr">
+        <is>
+          <t>P75</t>
+        </is>
+      </c>
+      <c r="F63" s="218" t="inlineStr">
+        <is>
+          <t>P90</t>
+        </is>
+      </c>
+      <c r="G63" s="218" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="125">
+      <c r="A64" s="214" t="inlineStr">
+        <is>
+          <t>Exit (5.5x ARR)</t>
+        </is>
+      </c>
+      <c r="B64" s="216" t="n">
+        <v>137095457</v>
+      </c>
+      <c r="C64" s="216" t="n">
+        <v>154379983</v>
+      </c>
+      <c r="D64" s="216" t="n">
+        <v>187303250</v>
+      </c>
+      <c r="E64" s="216" t="n">
+        <v>246132461</v>
+      </c>
+      <c r="F64" s="216" t="n">
+        <v>305525966</v>
+      </c>
+      <c r="G64" s="214" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="125">
+      <c r="A65" s="157" t="inlineStr">
+        <is>
+          <t>EUR 100M+ exit prob</t>
+        </is>
+      </c>
+      <c r="B65" s="157" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="C65" s="157" t="n"/>
+      <c r="D65" s="157" t="inlineStr">
+        <is>
+          <t>P10 is EUR 137M at 5.5x. Highly likely to clear EUR 100M.</t>
+        </is>
+      </c>
+      <c r="E65" s="157" t="n"/>
+      <c r="F65" s="157" t="n"/>
+      <c r="G65" s="157" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="125">
+      <c r="A67" s="163" t="inlineStr">
+        <is>
+          <t>AI-NATIVE EFFICIENCY METRICS</t>
+        </is>
+      </c>
+      <c r="B67" s="164" t="n"/>
+      <c r="C67" s="164" t="n"/>
+      <c r="D67" s="164" t="n"/>
+      <c r="E67" s="164" t="n"/>
+      <c r="F67" s="164" t="n"/>
+      <c r="G67" s="164" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="125">
+      <c r="A68" s="214" t="inlineStr">
+        <is>
+          <t>Max team size</t>
+        </is>
+      </c>
+      <c r="B68" s="216" t="n">
+        <v>18</v>
+      </c>
+      <c r="C68" s="214" t="n"/>
+      <c r="D68" s="214" t="inlineStr">
+        <is>
+          <t>vs 8 (operator) or 60 (full VC). AI replaces headcount.</t>
+        </is>
+      </c>
+      <c r="E68" s="214" t="n"/>
+      <c r="F68" s="214" t="n"/>
+      <c r="G68" s="214" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="125">
+      <c r="A69" s="157" t="inlineStr">
+        <is>
+          <t>Rev/employee (P50)</t>
+        </is>
+      </c>
+      <c r="B69" s="215" t="n">
+        <v>1891952</v>
+      </c>
+      <c r="C69" s="157" t="n"/>
+      <c r="D69" s="157" t="inlineStr">
+        <is>
+          <t>EUR 34M ARR / 18 people. Best-in-class vertical SaaS.</t>
+        </is>
+      </c>
+      <c r="E69" s="157" t="n"/>
+      <c r="F69" s="157" t="n"/>
+      <c r="G69" s="157" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" s="125">
+      <c r="A70" s="214" t="inlineStr">
+        <is>
+          <t>Capital efficiency</t>
+        </is>
+      </c>
+      <c r="B70" s="214" t="inlineStr">
+        <is>
+          <t>8.0x</t>
+        </is>
+      </c>
+      <c r="C70" s="214" t="n"/>
+      <c r="D70" s="214" t="inlineStr">
+        <is>
+          <t>EUR 34M ARR on EUR 4.3M total capital.</t>
+        </is>
+      </c>
+      <c r="E70" s="214" t="n"/>
+      <c r="F70" s="214" t="n"/>
+      <c r="G70" s="214" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" s="125">
+      <c r="A71" s="157" t="inlineStr">
+        <is>
+          <t>vs Path B (full VC)</t>
+        </is>
+      </c>
+      <c r="B71" s="157" t="inlineStr">
+        <is>
+          <t>60 people</t>
+        </is>
+      </c>
+      <c r="C71" s="157" t="n"/>
+      <c r="D71" s="157" t="inlineStr">
+        <is>
+          <t>EUR 99M ARR but EUR 42M capital and 60 team.</t>
+        </is>
+      </c>
+      <c r="E71" s="157" t="n"/>
+      <c r="F71" s="157" t="n"/>
+      <c r="G71" s="157" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1" s="125">
+      <c r="A73" s="163" t="inlineStr">
+        <is>
+          <t>SCENARIO NARRATIVE</t>
+        </is>
+      </c>
+      <c r="B73" s="164" t="n"/>
+      <c r="C73" s="164" t="n"/>
+      <c r="D73" s="164" t="n"/>
+      <c r="E73" s="164" t="n"/>
+      <c r="F73" s="164" t="n"/>
+      <c r="G73" s="164" t="n"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="125">
+      <c r="A74" s="211" t="inlineStr">
+        <is>
+          <t>Path C is the recommended strategic path. Same early trajectory as operator-seeded (M1-24 identical).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="125">
+      <c r="A75" s="211" t="inlineStr">
+        <is>
+          <t>EUR 4M strategic raise at M27 from a hospitality-specific investor (not a generalist VC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="125">
+      <c r="A76" s="211" t="inlineStr">
+        <is>
+          <t>Capital buys: faster PMS integrations, accelerated GTM (5 markets vs 2), portfolio expansion deals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="125">
+      <c r="A77" s="211" t="inlineStr">
+        <is>
+          <t>Team grows to 18 (not 60) — AI-native model means margin stays high (66-75%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="125">
+      <c r="A78" s="211" t="inlineStr">
+        <is>
+          <t>M36 P50: 502 hotels, EUR 16.7M ARR. M60 P50: 886 hotels, EUR 34M ARR, EUR 187M exit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="125">
+      <c r="A79" s="211" t="inlineStr">
+        <is>
+          <t>NOTE: M33+ numbers assume group rollouts landing. Conservative read: cap at 300-400 hotels M36.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
 </file>